--- a/academias/Humanidades - Estadisticos 20241.xlsx
+++ b/academias/Humanidades - Estadisticos 20241.xlsx
@@ -739,16 +739,16 @@
         <v>34</v>
       </c>
       <c r="E7">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F7">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G7" s="1">
-        <v>55.9</v>
+        <v>58.8</v>
       </c>
       <c r="H7" s="1">
-        <v>44.1</v>
+        <v>41.2</v>
       </c>
       <c r="I7" s="2">
         <v>5.4</v>
@@ -911,16 +911,16 @@
         <v>134</v>
       </c>
       <c r="E12">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="F12">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G12" s="1">
-        <v>76.90000000000001</v>
+        <v>77.59999999999999</v>
       </c>
       <c r="H12" s="1">
-        <v>23.1</v>
+        <v>22.4</v>
       </c>
       <c r="I12" s="2">
         <v>6.2</v>
@@ -1290,19 +1290,19 @@
         <v>37</v>
       </c>
       <c r="E23">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="F23">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G23" s="1">
-        <v>81.09999999999999</v>
+        <v>83.8</v>
       </c>
       <c r="H23" s="1">
-        <v>18.9</v>
+        <v>16.2</v>
       </c>
       <c r="I23" s="2">
-        <v>7.8</v>
+        <v>7.9</v>
       </c>
       <c r="J23">
         <v>0</v>
@@ -1407,7 +1407,7 @@
         <v>5.7</v>
       </c>
       <c r="I26" s="2">
-        <v>8.800000000000001</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="J26">
         <v>0</v>
@@ -1427,16 +1427,16 @@
         <v>306</v>
       </c>
       <c r="E27">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="F27">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="G27" s="1">
-        <v>86.3</v>
+        <v>86.59999999999999</v>
       </c>
       <c r="H27" s="1">
-        <v>13.7</v>
+        <v>13.4</v>
       </c>
       <c r="I27" s="2">
         <v>8.199999999999999</v>
@@ -1523,16 +1523,16 @@
         <v>664</v>
       </c>
       <c r="E30">
-        <v>553</v>
+        <v>555</v>
       </c>
       <c r="F30">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="G30" s="1">
-        <v>83.3</v>
+        <v>83.59999999999999</v>
       </c>
       <c r="H30" s="1">
-        <v>16.7</v>
+        <v>16.4</v>
       </c>
       <c r="I30" s="2">
         <v>7.6</v>
@@ -1781,25 +1781,25 @@
         <v>34</v>
       </c>
       <c r="E7">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="F7">
-        <v>34</v>
+        <v>17</v>
       </c>
       <c r="G7" s="1">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="H7" s="1">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="I7" s="2">
-        <v>0</v>
+        <v>6.1</v>
       </c>
       <c r="J7">
-        <v>34</v>
+        <v>0</v>
       </c>
       <c r="K7" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:11">
@@ -1816,25 +1816,25 @@
         <v>33</v>
       </c>
       <c r="E8">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="F8">
-        <v>33</v>
+        <v>8</v>
       </c>
       <c r="G8" s="1">
-        <v>0</v>
+        <v>75.8</v>
       </c>
       <c r="H8" s="1">
-        <v>100</v>
+        <v>24.2</v>
       </c>
       <c r="I8" s="2">
-        <v>0</v>
+        <v>7.3</v>
       </c>
       <c r="J8">
-        <v>33</v>
+        <v>0</v>
       </c>
       <c r="K8" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9" spans="1:11">
@@ -1851,25 +1851,25 @@
         <v>23</v>
       </c>
       <c r="E9">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="F9">
-        <v>23</v>
+        <v>13</v>
       </c>
       <c r="G9" s="1">
-        <v>0</v>
+        <v>43.5</v>
       </c>
       <c r="H9" s="1">
-        <v>100</v>
+        <v>56.5</v>
       </c>
       <c r="I9" s="2">
-        <v>0</v>
+        <v>5.8</v>
       </c>
       <c r="J9">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="K9" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10" spans="1:11">
@@ -1886,25 +1886,25 @@
         <v>19</v>
       </c>
       <c r="E10">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="F10">
-        <v>19</v>
+        <v>2</v>
       </c>
       <c r="G10" s="1">
-        <v>0</v>
+        <v>89.5</v>
       </c>
       <c r="H10" s="1">
-        <v>100</v>
+        <v>10.5</v>
       </c>
       <c r="I10" s="2">
-        <v>0</v>
+        <v>7.4</v>
       </c>
       <c r="J10">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="K10" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11" spans="1:11">
@@ -1921,25 +1921,25 @@
         <v>25</v>
       </c>
       <c r="E11">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="F11">
-        <v>25</v>
+        <v>3</v>
       </c>
       <c r="G11" s="1">
-        <v>0</v>
+        <v>88</v>
       </c>
       <c r="H11" s="1">
-        <v>100</v>
+        <v>12</v>
       </c>
       <c r="I11" s="2">
-        <v>0</v>
+        <v>6.9</v>
       </c>
       <c r="J11">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="K11" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12" spans="1:11">
@@ -1953,25 +1953,25 @@
         <v>134</v>
       </c>
       <c r="E12">
-        <v>0</v>
+        <v>91</v>
       </c>
       <c r="F12">
-        <v>134</v>
+        <v>43</v>
       </c>
       <c r="G12" s="1">
-        <v>0</v>
+        <v>67.90000000000001</v>
       </c>
       <c r="H12" s="1">
-        <v>100</v>
+        <v>32.1</v>
       </c>
       <c r="I12" s="2">
-        <v>0</v>
+        <v>6.7</v>
       </c>
       <c r="J12">
-        <v>134</v>
+        <v>0</v>
       </c>
       <c r="K12" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13" spans="1:11">
@@ -1988,25 +1988,25 @@
         <v>10</v>
       </c>
       <c r="E13">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="F13">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="G13" s="1">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H13" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="I13" s="2">
-        <v>0</v>
+        <v>9.6</v>
       </c>
       <c r="J13">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="K13" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14" spans="1:11">
@@ -2020,25 +2020,25 @@
         <v>10</v>
       </c>
       <c r="E14">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="F14">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="G14" s="1">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H14" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="I14" s="2">
-        <v>0</v>
+        <v>9.6</v>
       </c>
       <c r="J14">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="K14" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15" spans="1:11">
@@ -2055,25 +2055,25 @@
         <v>21</v>
       </c>
       <c r="E15">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="F15">
-        <v>21</v>
+        <v>6</v>
       </c>
       <c r="G15" s="1">
-        <v>0</v>
+        <v>71.40000000000001</v>
       </c>
       <c r="H15" s="1">
-        <v>100</v>
+        <v>28.6</v>
       </c>
       <c r="I15" s="2">
-        <v>0</v>
+        <v>7.2</v>
       </c>
       <c r="J15">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="K15" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16" spans="1:11">
@@ -2090,25 +2090,25 @@
         <v>19</v>
       </c>
       <c r="E16">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="F16">
-        <v>19</v>
+        <v>2</v>
       </c>
       <c r="G16" s="1">
-        <v>0</v>
+        <v>89.5</v>
       </c>
       <c r="H16" s="1">
-        <v>100</v>
+        <v>10.5</v>
       </c>
       <c r="I16" s="2">
-        <v>0</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J16">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="K16" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17" spans="1:11">
@@ -2125,25 +2125,25 @@
         <v>21</v>
       </c>
       <c r="E17">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="F17">
-        <v>21</v>
+        <v>3</v>
       </c>
       <c r="G17" s="1">
-        <v>0</v>
+        <v>85.7</v>
       </c>
       <c r="H17" s="1">
-        <v>100</v>
+        <v>14.3</v>
       </c>
       <c r="I17" s="2">
-        <v>0</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J17">
-        <v>21</v>
+        <v>1</v>
       </c>
       <c r="K17" s="1">
-        <v>100</v>
+        <v>4.76</v>
       </c>
     </row>
     <row r="18" spans="1:11">
@@ -2157,25 +2157,25 @@
         <v>61</v>
       </c>
       <c r="E18">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="F18">
-        <v>61</v>
+        <v>11</v>
       </c>
       <c r="G18" s="1">
-        <v>0</v>
+        <v>82</v>
       </c>
       <c r="H18" s="1">
-        <v>100</v>
+        <v>18</v>
       </c>
       <c r="I18" s="2">
-        <v>0</v>
+        <v>7.9</v>
       </c>
       <c r="J18">
-        <v>61</v>
+        <v>1</v>
       </c>
       <c r="K18" s="1">
-        <v>100</v>
+        <v>1.6</v>
       </c>
     </row>
     <row r="19" spans="1:11">
@@ -2192,25 +2192,25 @@
         <v>40</v>
       </c>
       <c r="E19">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="F19">
-        <v>40</v>
+        <v>4</v>
       </c>
       <c r="G19" s="1">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="H19" s="1">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="I19" s="2">
-        <v>0</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J19">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="K19" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20" spans="1:11">
@@ -2227,25 +2227,25 @@
         <v>41</v>
       </c>
       <c r="E20">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="F20">
-        <v>41</v>
+        <v>9</v>
       </c>
       <c r="G20" s="1">
-        <v>0</v>
+        <v>78</v>
       </c>
       <c r="H20" s="1">
-        <v>100</v>
+        <v>22</v>
       </c>
       <c r="I20" s="2">
-        <v>0</v>
+        <v>7.1</v>
       </c>
       <c r="J20">
-        <v>41</v>
+        <v>0</v>
       </c>
       <c r="K20" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21" spans="1:11">
@@ -2262,25 +2262,25 @@
         <v>48</v>
       </c>
       <c r="E21">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="F21">
-        <v>48</v>
+        <v>4</v>
       </c>
       <c r="G21" s="1">
-        <v>0</v>
+        <v>91.7</v>
       </c>
       <c r="H21" s="1">
-        <v>100</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="I21" s="2">
-        <v>0</v>
+        <v>7.6</v>
       </c>
       <c r="J21">
-        <v>48</v>
+        <v>0</v>
       </c>
       <c r="K21" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22" spans="1:11">
@@ -2297,25 +2297,25 @@
         <v>36</v>
       </c>
       <c r="E22">
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="F22">
-        <v>36</v>
+        <v>1</v>
       </c>
       <c r="G22" s="1">
-        <v>0</v>
+        <v>97.2</v>
       </c>
       <c r="H22" s="1">
-        <v>100</v>
+        <v>2.8</v>
       </c>
       <c r="I22" s="2">
-        <v>0</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="J22">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="K22" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23" spans="1:11">
@@ -2332,25 +2332,25 @@
         <v>37</v>
       </c>
       <c r="E23">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="F23">
-        <v>37</v>
+        <v>7</v>
       </c>
       <c r="G23" s="1">
-        <v>0</v>
+        <v>81.09999999999999</v>
       </c>
       <c r="H23" s="1">
-        <v>100</v>
+        <v>18.9</v>
       </c>
       <c r="I23" s="2">
-        <v>0</v>
+        <v>7.3</v>
       </c>
       <c r="J23">
-        <v>37</v>
+        <v>0</v>
       </c>
       <c r="K23" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="24" spans="1:11">
@@ -2367,25 +2367,25 @@
         <v>33</v>
       </c>
       <c r="E24">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="F24">
-        <v>33</v>
+        <v>4</v>
       </c>
       <c r="G24" s="1">
-        <v>0</v>
+        <v>87.90000000000001</v>
       </c>
       <c r="H24" s="1">
-        <v>100</v>
+        <v>12.1</v>
       </c>
       <c r="I24" s="2">
-        <v>0</v>
+        <v>8.1</v>
       </c>
       <c r="J24">
-        <v>33</v>
+        <v>0</v>
       </c>
       <c r="K24" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="25" spans="1:11">
@@ -2402,25 +2402,25 @@
         <v>36</v>
       </c>
       <c r="E25">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="F25">
-        <v>36</v>
+        <v>2</v>
       </c>
       <c r="G25" s="1">
-        <v>0</v>
+        <v>94.40000000000001</v>
       </c>
       <c r="H25" s="1">
-        <v>100</v>
+        <v>5.6</v>
       </c>
       <c r="I25" s="2">
-        <v>0</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="J25">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="K25" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="26" spans="1:11">
@@ -2437,25 +2437,25 @@
         <v>35</v>
       </c>
       <c r="E26">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="F26">
-        <v>35</v>
+        <v>1</v>
       </c>
       <c r="G26" s="1">
-        <v>0</v>
+        <v>97.09999999999999</v>
       </c>
       <c r="H26" s="1">
-        <v>100</v>
+        <v>2.9</v>
       </c>
       <c r="I26" s="2">
-        <v>0</v>
+        <v>8.6</v>
       </c>
       <c r="J26">
-        <v>35</v>
+        <v>0</v>
       </c>
       <c r="K26" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="27" spans="1:11">
@@ -2469,25 +2469,25 @@
         <v>306</v>
       </c>
       <c r="E27">
-        <v>0</v>
+        <v>274</v>
       </c>
       <c r="F27">
-        <v>306</v>
+        <v>32</v>
       </c>
       <c r="G27" s="1">
-        <v>0</v>
+        <v>89.5</v>
       </c>
       <c r="H27" s="1">
-        <v>100</v>
+        <v>10.5</v>
       </c>
       <c r="I27" s="2">
-        <v>0</v>
+        <v>7.9</v>
       </c>
       <c r="J27">
-        <v>306</v>
+        <v>0</v>
       </c>
       <c r="K27" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="28" spans="1:11">
@@ -2504,25 +2504,25 @@
         <v>40</v>
       </c>
       <c r="E28">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="F28">
-        <v>40</v>
+        <v>22</v>
       </c>
       <c r="G28" s="1">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="H28" s="1">
-        <v>100</v>
+        <v>55</v>
       </c>
       <c r="I28" s="2">
-        <v>0</v>
+        <v>5.7</v>
       </c>
       <c r="J28">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="K28" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="29" spans="1:11">
@@ -2536,25 +2536,25 @@
         <v>40</v>
       </c>
       <c r="E29">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="F29">
-        <v>40</v>
+        <v>22</v>
       </c>
       <c r="G29" s="1">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="H29" s="1">
-        <v>100</v>
+        <v>55</v>
       </c>
       <c r="I29" s="2">
-        <v>0</v>
+        <v>5.7</v>
       </c>
       <c r="J29">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="K29" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="30" spans="1:11">
@@ -2565,25 +2565,25 @@
         <v>664</v>
       </c>
       <c r="E30">
-        <v>0</v>
+        <v>443</v>
       </c>
       <c r="F30">
-        <v>664</v>
+        <v>221</v>
       </c>
       <c r="G30" s="1">
-        <v>0</v>
+        <v>66.7</v>
       </c>
       <c r="H30" s="1">
-        <v>100</v>
+        <v>33.3</v>
       </c>
       <c r="I30" s="2">
-        <v>0</v>
+        <v>6.2</v>
       </c>
       <c r="J30">
-        <v>664</v>
+        <v>114</v>
       </c>
       <c r="K30" s="1">
-        <v>100</v>
+        <v>17.2</v>
       </c>
     </row>
   </sheetData>
@@ -2823,19 +2823,19 @@
         <v>34</v>
       </c>
       <c r="E7">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="F7">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="G7" s="1">
-        <v>55.9</v>
+        <v>50</v>
       </c>
       <c r="H7" s="1">
-        <v>44.1</v>
+        <v>50</v>
       </c>
       <c r="I7" s="2">
-        <v>5.8</v>
+        <v>6.1</v>
       </c>
       <c r="J7">
         <v>0</v>
@@ -2858,19 +2858,19 @@
         <v>33</v>
       </c>
       <c r="E8">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="F8">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="G8" s="1">
-        <v>81.8</v>
+        <v>75.8</v>
       </c>
       <c r="H8" s="1">
-        <v>18.2</v>
+        <v>24.2</v>
       </c>
       <c r="I8" s="2">
-        <v>6.2</v>
+        <v>6.9</v>
       </c>
       <c r="J8">
         <v>0</v>
@@ -2893,19 +2893,19 @@
         <v>23</v>
       </c>
       <c r="E9">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="F9">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="G9" s="1">
-        <v>78.3</v>
+        <v>43.5</v>
       </c>
       <c r="H9" s="1">
-        <v>21.7</v>
+        <v>56.5</v>
       </c>
       <c r="I9" s="2">
-        <v>6.1</v>
+        <v>5.9</v>
       </c>
       <c r="J9">
         <v>0</v>
@@ -2940,7 +2940,7 @@
         <v>10.5</v>
       </c>
       <c r="I10" s="2">
-        <v>6.8</v>
+        <v>7.3</v>
       </c>
       <c r="J10">
         <v>0</v>
@@ -2975,7 +2975,7 @@
         <v>12</v>
       </c>
       <c r="I11" s="2">
-        <v>7.2</v>
+        <v>7.3</v>
       </c>
       <c r="J11">
         <v>0</v>
@@ -2995,19 +2995,19 @@
         <v>134</v>
       </c>
       <c r="E12">
-        <v>103</v>
+        <v>91</v>
       </c>
       <c r="F12">
-        <v>31</v>
+        <v>43</v>
       </c>
       <c r="G12" s="1">
-        <v>76.90000000000001</v>
+        <v>67.90000000000001</v>
       </c>
       <c r="H12" s="1">
-        <v>23.1</v>
+        <v>32.1</v>
       </c>
       <c r="I12" s="2">
-        <v>6.4</v>
+        <v>6.7</v>
       </c>
       <c r="J12">
         <v>0</v>
@@ -3042,7 +3042,7 @@
         <v>0</v>
       </c>
       <c r="I13" s="2">
-        <v>8.800000000000001</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="J13">
         <v>0</v>
@@ -3074,7 +3074,7 @@
         <v>0</v>
       </c>
       <c r="I14" s="2">
-        <v>8.800000000000001</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="J14">
         <v>0</v>
@@ -3109,7 +3109,7 @@
         <v>28.6</v>
       </c>
       <c r="I15" s="2">
-        <v>6.4</v>
+        <v>6.9</v>
       </c>
       <c r="J15">
         <v>0</v>
@@ -3179,7 +3179,7 @@
         <v>9.5</v>
       </c>
       <c r="I17" s="2">
-        <v>8.1</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J17">
         <v>0</v>
@@ -3211,7 +3211,7 @@
         <v>16.4</v>
       </c>
       <c r="I18" s="2">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="J18">
         <v>0</v>
@@ -3234,19 +3234,19 @@
         <v>40</v>
       </c>
       <c r="E19">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="F19">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="G19" s="1">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="H19" s="1">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="I19" s="2">
-        <v>8.4</v>
+        <v>8.5</v>
       </c>
       <c r="J19">
         <v>0</v>
@@ -3269,19 +3269,19 @@
         <v>41</v>
       </c>
       <c r="E20">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="F20">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="G20" s="1">
-        <v>70.7</v>
+        <v>78</v>
       </c>
       <c r="H20" s="1">
-        <v>29.3</v>
+        <v>22</v>
       </c>
       <c r="I20" s="2">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="J20">
         <v>0</v>
@@ -3304,19 +3304,19 @@
         <v>48</v>
       </c>
       <c r="E21">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="F21">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G21" s="1">
-        <v>93.8</v>
+        <v>91.7</v>
       </c>
       <c r="H21" s="1">
-        <v>6.2</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="I21" s="2">
-        <v>8.300000000000001</v>
+        <v>8.1</v>
       </c>
       <c r="J21">
         <v>0</v>
@@ -3409,19 +3409,19 @@
         <v>33</v>
       </c>
       <c r="E24">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="F24">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="G24" s="1">
-        <v>81.8</v>
+        <v>87.90000000000001</v>
       </c>
       <c r="H24" s="1">
-        <v>18.2</v>
+        <v>12.1</v>
       </c>
       <c r="I24" s="2">
-        <v>7.8</v>
+        <v>8.1</v>
       </c>
       <c r="J24">
         <v>0</v>
@@ -3444,19 +3444,19 @@
         <v>36</v>
       </c>
       <c r="E25">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="F25">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="G25" s="1">
-        <v>86.09999999999999</v>
+        <v>94.40000000000001</v>
       </c>
       <c r="H25" s="1">
-        <v>13.9</v>
+        <v>5.6</v>
       </c>
       <c r="I25" s="2">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="J25">
         <v>0</v>
@@ -3479,19 +3479,19 @@
         <v>35</v>
       </c>
       <c r="E26">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="F26">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G26" s="1">
-        <v>94.3</v>
+        <v>97.09999999999999</v>
       </c>
       <c r="H26" s="1">
-        <v>5.7</v>
+        <v>2.9</v>
       </c>
       <c r="I26" s="2">
-        <v>8.699999999999999</v>
+        <v>8.9</v>
       </c>
       <c r="J26">
         <v>0</v>
@@ -3511,19 +3511,19 @@
         <v>306</v>
       </c>
       <c r="E27">
-        <v>264</v>
+        <v>274</v>
       </c>
       <c r="F27">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="G27" s="1">
-        <v>86.3</v>
+        <v>89.5</v>
       </c>
       <c r="H27" s="1">
-        <v>13.7</v>
+        <v>10.5</v>
       </c>
       <c r="I27" s="2">
-        <v>8.199999999999999</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="J27">
         <v>0</v>
@@ -3546,19 +3546,19 @@
         <v>40</v>
       </c>
       <c r="E28">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F28">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="G28" s="1">
-        <v>42.5</v>
+        <v>45</v>
       </c>
       <c r="H28" s="1">
-        <v>57.5</v>
+        <v>55</v>
       </c>
       <c r="I28" s="2">
-        <v>6</v>
+        <v>5.8</v>
       </c>
       <c r="J28">
         <v>0</v>
@@ -3578,19 +3578,19 @@
         <v>40</v>
       </c>
       <c r="E29">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F29">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="G29" s="1">
-        <v>42.5</v>
+        <v>45</v>
       </c>
       <c r="H29" s="1">
-        <v>57.5</v>
+        <v>55</v>
       </c>
       <c r="I29" s="2">
-        <v>6</v>
+        <v>5.8</v>
       </c>
       <c r="J29">
         <v>0</v>
@@ -3607,19 +3607,19 @@
         <v>664</v>
       </c>
       <c r="E30">
-        <v>553</v>
+        <v>552</v>
       </c>
       <c r="F30">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="G30" s="1">
-        <v>83.3</v>
+        <v>83.09999999999999</v>
       </c>
       <c r="H30" s="1">
-        <v>16.7</v>
+        <v>16.9</v>
       </c>
       <c r="I30" s="2">
-        <v>7.7</v>
+        <v>7.8</v>
       </c>
       <c r="J30">
         <v>0</v>

--- a/academias/Humanidades - Estadisticos 20241.xlsx
+++ b/academias/Humanidades - Estadisticos 20241.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="270" uniqueCount="43">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="276" uniqueCount="44">
   <si>
     <t>Docente</t>
   </si>
@@ -51,18 +51,21 @@
     <t>por_blancos</t>
   </si>
   <si>
+    <t>Breniz Camarillo Lysette</t>
+  </si>
+  <si>
     <t>Castro Vasquez Julieta</t>
   </si>
   <si>
     <t>Gaspar Velazco Juan Francisco</t>
   </si>
   <si>
-    <t>Hernández Mendoza Delfina</t>
-  </si>
-  <si>
     <t>Martínez López Miguel Ángel</t>
   </si>
   <si>
+    <t>Martínez Marañon Mauricio</t>
+  </si>
+  <si>
     <t>Ochoa Martínez Mayeli</t>
   </si>
   <si>
@@ -81,43 +84,43 @@
     <t>Totales Generales</t>
   </si>
   <si>
+    <t>3ASV</t>
+  </si>
+  <si>
     <t>3AEM</t>
   </si>
   <si>
+    <t>3BEM</t>
+  </si>
+  <si>
+    <t>3BLCM</t>
+  </si>
+  <si>
+    <t>1BV</t>
+  </si>
+  <si>
+    <t>1CV</t>
+  </si>
+  <si>
+    <t>1DV</t>
+  </si>
+  <si>
+    <t>1EV</t>
+  </si>
+  <si>
+    <t>3ALCV</t>
+  </si>
+  <si>
+    <t>3AEV</t>
+  </si>
+  <si>
+    <t>3APV</t>
+  </si>
+  <si>
+    <t>3ARHV</t>
+  </si>
+  <si>
     <t>3APM</t>
-  </si>
-  <si>
-    <t>3BEM</t>
-  </si>
-  <si>
-    <t>3BLCM</t>
-  </si>
-  <si>
-    <t>1BV</t>
-  </si>
-  <si>
-    <t>1CV</t>
-  </si>
-  <si>
-    <t>1DV</t>
-  </si>
-  <si>
-    <t>1EV</t>
-  </si>
-  <si>
-    <t>3ALCV</t>
-  </si>
-  <si>
-    <t>3ASV</t>
-  </si>
-  <si>
-    <t>3AEV</t>
-  </si>
-  <si>
-    <t>3APV</t>
-  </si>
-  <si>
-    <t>3ARHV</t>
   </si>
   <si>
     <t>1AM</t>
@@ -508,7 +511,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:K30"/>
+  <dimension ref="A1:K31"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -558,28 +561,28 @@
         <v>11</v>
       </c>
       <c r="B2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C2" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D2">
-        <v>24</v>
+        <v>10</v>
       </c>
       <c r="E2">
-        <v>23</v>
+        <v>10</v>
       </c>
       <c r="F2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G2" s="1">
-        <v>95.8</v>
+        <v>100</v>
       </c>
       <c r="H2" s="1">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="I2" s="2">
-        <v>8.300000000000001</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="J2">
         <v>0</v>
@@ -593,28 +596,25 @@
         <v>11</v>
       </c>
       <c r="B3" t="s">
-        <v>17</v>
-      </c>
-      <c r="C3" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="D3">
-        <v>28</v>
+        <v>10</v>
       </c>
       <c r="E3">
-        <v>27</v>
+        <v>10</v>
       </c>
       <c r="F3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G3" s="1">
-        <v>96.40000000000001</v>
+        <v>100</v>
       </c>
       <c r="H3" s="1">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="I3" s="2">
-        <v>8.9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="J3">
         <v>0</v>
@@ -625,10 +625,10 @@
     </row>
     <row r="4" spans="1:11">
       <c r="A4" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B4" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C4" t="s">
         <v>23</v>
@@ -649,7 +649,7 @@
         <v>4.2</v>
       </c>
       <c r="I4" s="2">
-        <v>8.4</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="J4">
         <v>0</v>
@@ -660,31 +660,31 @@
     </row>
     <row r="5" spans="1:11">
       <c r="A5" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B5" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C5" t="s">
         <v>24</v>
       </c>
       <c r="D5">
-        <v>37</v>
+        <v>24</v>
       </c>
       <c r="E5">
-        <v>35</v>
+        <v>23</v>
       </c>
       <c r="F5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G5" s="1">
-        <v>94.59999999999999</v>
+        <v>95.8</v>
       </c>
       <c r="H5" s="1">
-        <v>5.4</v>
+        <v>4.2</v>
       </c>
       <c r="I5" s="2">
-        <v>8.300000000000001</v>
+        <v>8.4</v>
       </c>
       <c r="J5">
         <v>0</v>
@@ -695,28 +695,31 @@
     </row>
     <row r="6" spans="1:11">
       <c r="A6" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B6" t="s">
         <v>18</v>
       </c>
+      <c r="C6" t="s">
+        <v>25</v>
+      </c>
       <c r="D6">
-        <v>113</v>
+        <v>37</v>
       </c>
       <c r="E6">
-        <v>108</v>
+        <v>35</v>
       </c>
       <c r="F6">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="G6" s="1">
-        <v>95.59999999999999</v>
+        <v>94.59999999999999</v>
       </c>
       <c r="H6" s="1">
-        <v>4.4</v>
+        <v>5.4</v>
       </c>
       <c r="I6" s="2">
-        <v>8.5</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="J6">
         <v>0</v>
@@ -732,26 +735,23 @@
       <c r="B7" t="s">
         <v>19</v>
       </c>
-      <c r="C7" t="s">
-        <v>25</v>
-      </c>
       <c r="D7">
-        <v>34</v>
+        <v>85</v>
       </c>
       <c r="E7">
-        <v>20</v>
+        <v>81</v>
       </c>
       <c r="F7">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="G7" s="1">
-        <v>58.8</v>
+        <v>95.3</v>
       </c>
       <c r="H7" s="1">
-        <v>41.2</v>
+        <v>4.7</v>
       </c>
       <c r="I7" s="2">
-        <v>5.4</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="J7">
         <v>0</v>
@@ -762,31 +762,31 @@
     </row>
     <row r="8" spans="1:11">
       <c r="A8" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B8" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C8" t="s">
         <v>26</v>
       </c>
       <c r="D8">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="E8">
-        <v>27</v>
+        <v>20</v>
       </c>
       <c r="F8">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="G8" s="1">
-        <v>81.8</v>
+        <v>58.8</v>
       </c>
       <c r="H8" s="1">
-        <v>18.2</v>
+        <v>41.2</v>
       </c>
       <c r="I8" s="2">
-        <v>6</v>
+        <v>5.4</v>
       </c>
       <c r="J8">
         <v>0</v>
@@ -797,28 +797,28 @@
     </row>
     <row r="9" spans="1:11">
       <c r="A9" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B9" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C9" t="s">
         <v>27</v>
       </c>
       <c r="D9">
-        <v>23</v>
+        <v>33</v>
       </c>
       <c r="E9">
-        <v>18</v>
+        <v>27</v>
       </c>
       <c r="F9">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G9" s="1">
-        <v>78.3</v>
+        <v>81.8</v>
       </c>
       <c r="H9" s="1">
-        <v>21.7</v>
+        <v>18.2</v>
       </c>
       <c r="I9" s="2">
         <v>6</v>
@@ -832,31 +832,31 @@
     </row>
     <row r="10" spans="1:11">
       <c r="A10" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B10" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C10" t="s">
         <v>28</v>
       </c>
       <c r="D10">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="E10">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F10">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="G10" s="1">
-        <v>89.5</v>
+        <v>78.3</v>
       </c>
       <c r="H10" s="1">
-        <v>10.5</v>
+        <v>21.7</v>
       </c>
       <c r="I10" s="2">
-        <v>6.7</v>
+        <v>6</v>
       </c>
       <c r="J10">
         <v>0</v>
@@ -867,31 +867,31 @@
     </row>
     <row r="11" spans="1:11">
       <c r="A11" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B11" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="C11" t="s">
         <v>29</v>
       </c>
       <c r="D11">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="E11">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="F11">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G11" s="1">
-        <v>88</v>
+        <v>89.5</v>
       </c>
       <c r="H11" s="1">
-        <v>12</v>
+        <v>10.5</v>
       </c>
       <c r="I11" s="2">
-        <v>7</v>
+        <v>6.7</v>
       </c>
       <c r="J11">
         <v>0</v>
@@ -902,28 +902,31 @@
     </row>
     <row r="12" spans="1:11">
       <c r="A12" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B12" t="s">
         <v>18</v>
       </c>
+      <c r="C12" t="s">
+        <v>30</v>
+      </c>
       <c r="D12">
-        <v>134</v>
+        <v>25</v>
       </c>
       <c r="E12">
-        <v>104</v>
+        <v>22</v>
       </c>
       <c r="F12">
-        <v>30</v>
+        <v>3</v>
       </c>
       <c r="G12" s="1">
-        <v>77.59999999999999</v>
+        <v>88</v>
       </c>
       <c r="H12" s="1">
-        <v>22.4</v>
+        <v>12</v>
       </c>
       <c r="I12" s="2">
-        <v>6.2</v>
+        <v>7</v>
       </c>
       <c r="J12">
         <v>0</v>
@@ -937,28 +940,25 @@
         <v>13</v>
       </c>
       <c r="B13" t="s">
-        <v>17</v>
-      </c>
-      <c r="C13" t="s">
+        <v>19</v>
+      </c>
+      <c r="D13">
+        <v>134</v>
+      </c>
+      <c r="E13">
+        <v>104</v>
+      </c>
+      <c r="F13">
         <v>30</v>
       </c>
-      <c r="D13">
-        <v>10</v>
-      </c>
-      <c r="E13">
-        <v>10</v>
-      </c>
-      <c r="F13">
-        <v>0</v>
-      </c>
       <c r="G13" s="1">
-        <v>100</v>
+        <v>77.59999999999999</v>
       </c>
       <c r="H13" s="1">
-        <v>0</v>
+        <v>22.4</v>
       </c>
       <c r="I13" s="2">
-        <v>8.800000000000001</v>
+        <v>6.2</v>
       </c>
       <c r="J13">
         <v>0</v>
@@ -969,28 +969,31 @@
     </row>
     <row r="14" spans="1:11">
       <c r="A14" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B14" t="s">
         <v>18</v>
       </c>
+      <c r="C14" t="s">
+        <v>31</v>
+      </c>
       <c r="D14">
-        <v>10</v>
+        <v>21</v>
       </c>
       <c r="E14">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="F14">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="G14" s="1">
-        <v>100</v>
+        <v>71.40000000000001</v>
       </c>
       <c r="H14" s="1">
-        <v>0</v>
+        <v>28.6</v>
       </c>
       <c r="I14" s="2">
-        <v>8.800000000000001</v>
+        <v>6</v>
       </c>
       <c r="J14">
         <v>0</v>
@@ -1004,28 +1007,28 @@
         <v>14</v>
       </c>
       <c r="B15" t="s">
+        <v>18</v>
+      </c>
+      <c r="C15" t="s">
+        <v>32</v>
+      </c>
+      <c r="D15">
+        <v>19</v>
+      </c>
+      <c r="E15">
         <v>17</v>
       </c>
-      <c r="C15" t="s">
-        <v>31</v>
-      </c>
-      <c r="D15">
-        <v>21</v>
-      </c>
-      <c r="E15">
-        <v>15</v>
-      </c>
       <c r="F15">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="G15" s="1">
-        <v>71.40000000000001</v>
+        <v>89.5</v>
       </c>
       <c r="H15" s="1">
-        <v>28.6</v>
+        <v>10.5</v>
       </c>
       <c r="I15" s="2">
-        <v>6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J15">
         <v>0</v>
@@ -1039,28 +1042,28 @@
         <v>14</v>
       </c>
       <c r="B16" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C16" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D16">
+        <v>21</v>
+      </c>
+      <c r="E16">
         <v>19</v>
-      </c>
-      <c r="E16">
-        <v>17</v>
       </c>
       <c r="F16">
         <v>2</v>
       </c>
       <c r="G16" s="1">
-        <v>89.5</v>
+        <v>90.5</v>
       </c>
       <c r="H16" s="1">
-        <v>10.5</v>
+        <v>9.5</v>
       </c>
       <c r="I16" s="2">
-        <v>8.199999999999999</v>
+        <v>7.9</v>
       </c>
       <c r="J16">
         <v>0</v>
@@ -1074,28 +1077,25 @@
         <v>14</v>
       </c>
       <c r="B17" t="s">
-        <v>17</v>
-      </c>
-      <c r="C17" t="s">
-        <v>33</v>
+        <v>19</v>
       </c>
       <c r="D17">
-        <v>21</v>
+        <v>61</v>
       </c>
       <c r="E17">
-        <v>19</v>
+        <v>51</v>
       </c>
       <c r="F17">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="G17" s="1">
-        <v>90.5</v>
+        <v>83.59999999999999</v>
       </c>
       <c r="H17" s="1">
-        <v>9.5</v>
+        <v>16.4</v>
       </c>
       <c r="I17" s="2">
-        <v>7.9</v>
+        <v>7.4</v>
       </c>
       <c r="J17">
         <v>0</v>
@@ -1106,28 +1106,31 @@
     </row>
     <row r="18" spans="1:11">
       <c r="A18" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B18" t="s">
         <v>18</v>
       </c>
+      <c r="C18" t="s">
+        <v>34</v>
+      </c>
       <c r="D18">
-        <v>61</v>
+        <v>28</v>
       </c>
       <c r="E18">
-        <v>51</v>
+        <v>27</v>
       </c>
       <c r="F18">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="G18" s="1">
-        <v>83.59999999999999</v>
+        <v>96.40000000000001</v>
       </c>
       <c r="H18" s="1">
-        <v>16.4</v>
+        <v>3.6</v>
       </c>
       <c r="I18" s="2">
-        <v>7.4</v>
+        <v>8.9</v>
       </c>
       <c r="J18">
         <v>0</v>
@@ -1143,26 +1146,23 @@
       <c r="B19" t="s">
         <v>19</v>
       </c>
-      <c r="C19" t="s">
-        <v>34</v>
-      </c>
       <c r="D19">
-        <v>40</v>
+        <v>28</v>
       </c>
       <c r="E19">
-        <v>34</v>
+        <v>27</v>
       </c>
       <c r="F19">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="G19" s="1">
-        <v>85</v>
+        <v>96.40000000000001</v>
       </c>
       <c r="H19" s="1">
-        <v>15</v>
+        <v>3.6</v>
       </c>
       <c r="I19" s="2">
-        <v>8.4</v>
+        <v>8.9</v>
       </c>
       <c r="J19">
         <v>0</v>
@@ -1173,31 +1173,31 @@
     </row>
     <row r="20" spans="1:11">
       <c r="A20" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B20" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C20" t="s">
         <v>35</v>
       </c>
       <c r="D20">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E20">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="F20">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="G20" s="1">
-        <v>70.7</v>
+        <v>85</v>
       </c>
       <c r="H20" s="1">
-        <v>29.3</v>
+        <v>15</v>
       </c>
       <c r="I20" s="2">
-        <v>7.3</v>
+        <v>8.4</v>
       </c>
       <c r="J20">
         <v>0</v>
@@ -1208,31 +1208,31 @@
     </row>
     <row r="21" spans="1:11">
       <c r="A21" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B21" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C21" t="s">
         <v>36</v>
       </c>
       <c r="D21">
-        <v>48</v>
+        <v>41</v>
       </c>
       <c r="E21">
-        <v>45</v>
+        <v>29</v>
       </c>
       <c r="F21">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="G21" s="1">
-        <v>93.8</v>
+        <v>70.7</v>
       </c>
       <c r="H21" s="1">
-        <v>6.2</v>
+        <v>29.3</v>
       </c>
       <c r="I21" s="2">
-        <v>8.300000000000001</v>
+        <v>7.3</v>
       </c>
       <c r="J21">
         <v>0</v>
@@ -1243,31 +1243,31 @@
     </row>
     <row r="22" spans="1:11">
       <c r="A22" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B22" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C22" t="s">
         <v>37</v>
       </c>
       <c r="D22">
-        <v>36</v>
+        <v>48</v>
       </c>
       <c r="E22">
-        <v>35</v>
+        <v>45</v>
       </c>
       <c r="F22">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G22" s="1">
-        <v>97.2</v>
+        <v>93.8</v>
       </c>
       <c r="H22" s="1">
-        <v>2.8</v>
+        <v>6.2</v>
       </c>
       <c r="I22" s="2">
-        <v>8.699999999999999</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="J22">
         <v>0</v>
@@ -1278,31 +1278,31 @@
     </row>
     <row r="23" spans="1:11">
       <c r="A23" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B23" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C23" t="s">
         <v>38</v>
       </c>
       <c r="D23">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="E23">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="F23">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="G23" s="1">
-        <v>83.8</v>
+        <v>97.2</v>
       </c>
       <c r="H23" s="1">
-        <v>16.2</v>
+        <v>2.8</v>
       </c>
       <c r="I23" s="2">
-        <v>7.9</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="J23">
         <v>0</v>
@@ -1313,31 +1313,31 @@
     </row>
     <row r="24" spans="1:11">
       <c r="A24" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B24" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C24" t="s">
         <v>39</v>
       </c>
       <c r="D24">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="E24">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="F24">
         <v>6</v>
       </c>
       <c r="G24" s="1">
-        <v>81.8</v>
+        <v>83.8</v>
       </c>
       <c r="H24" s="1">
-        <v>18.2</v>
+        <v>16.2</v>
       </c>
       <c r="I24" s="2">
-        <v>7.8</v>
+        <v>7.9</v>
       </c>
       <c r="J24">
         <v>0</v>
@@ -1348,31 +1348,31 @@
     </row>
     <row r="25" spans="1:11">
       <c r="A25" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B25" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="C25" t="s">
         <v>40</v>
       </c>
       <c r="D25">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="E25">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="F25">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G25" s="1">
-        <v>86.09999999999999</v>
+        <v>81.8</v>
       </c>
       <c r="H25" s="1">
-        <v>13.9</v>
+        <v>18.2</v>
       </c>
       <c r="I25" s="2">
-        <v>8.4</v>
+        <v>7.8</v>
       </c>
       <c r="J25">
         <v>0</v>
@@ -1383,31 +1383,31 @@
     </row>
     <row r="26" spans="1:11">
       <c r="A26" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B26" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C26" t="s">
         <v>41</v>
       </c>
       <c r="D26">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E26">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="F26">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="G26" s="1">
-        <v>94.3</v>
+        <v>86.09999999999999</v>
       </c>
       <c r="H26" s="1">
-        <v>5.7</v>
+        <v>13.9</v>
       </c>
       <c r="I26" s="2">
-        <v>8.699999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="J26">
         <v>0</v>
@@ -1418,28 +1418,31 @@
     </row>
     <row r="27" spans="1:11">
       <c r="A27" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B27" t="s">
         <v>18</v>
       </c>
+      <c r="C27" t="s">
+        <v>42</v>
+      </c>
       <c r="D27">
-        <v>306</v>
+        <v>35</v>
       </c>
       <c r="E27">
-        <v>265</v>
+        <v>33</v>
       </c>
       <c r="F27">
-        <v>41</v>
+        <v>2</v>
       </c>
       <c r="G27" s="1">
-        <v>86.59999999999999</v>
+        <v>94.3</v>
       </c>
       <c r="H27" s="1">
-        <v>13.4</v>
+        <v>5.7</v>
       </c>
       <c r="I27" s="2">
-        <v>8.199999999999999</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="J27">
         <v>0</v>
@@ -1455,26 +1458,23 @@
       <c r="B28" t="s">
         <v>19</v>
       </c>
-      <c r="C28" t="s">
-        <v>42</v>
-      </c>
       <c r="D28">
-        <v>40</v>
+        <v>306</v>
       </c>
       <c r="E28">
-        <v>17</v>
+        <v>265</v>
       </c>
       <c r="F28">
-        <v>23</v>
+        <v>41</v>
       </c>
       <c r="G28" s="1">
-        <v>42.5</v>
+        <v>86.59999999999999</v>
       </c>
       <c r="H28" s="1">
-        <v>57.5</v>
+        <v>13.4</v>
       </c>
       <c r="I28" s="2">
-        <v>6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J28">
         <v>0</v>
@@ -1485,10 +1485,13 @@
     </row>
     <row r="29" spans="1:11">
       <c r="A29" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B29" t="s">
-        <v>18</v>
+        <v>20</v>
+      </c>
+      <c r="C29" t="s">
+        <v>43</v>
       </c>
       <c r="D29">
         <v>40</v>
@@ -1516,31 +1519,63 @@
       </c>
     </row>
     <row r="30" spans="1:11">
+      <c r="A30" t="s">
+        <v>17</v>
+      </c>
       <c r="B30" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D30">
+        <v>40</v>
+      </c>
+      <c r="E30">
+        <v>17</v>
+      </c>
+      <c r="F30">
+        <v>23</v>
+      </c>
+      <c r="G30" s="1">
+        <v>42.5</v>
+      </c>
+      <c r="H30" s="1">
+        <v>57.5</v>
+      </c>
+      <c r="I30" s="2">
+        <v>6</v>
+      </c>
+      <c r="J30">
+        <v>0</v>
+      </c>
+      <c r="K30" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="1:11">
+      <c r="B31" t="s">
+        <v>21</v>
+      </c>
+      <c r="D31">
         <v>664</v>
       </c>
-      <c r="E30">
+      <c r="E31">
         <v>555</v>
       </c>
-      <c r="F30">
+      <c r="F31">
         <v>109</v>
       </c>
-      <c r="G30" s="1">
+      <c r="G31" s="1">
         <v>83.59999999999999</v>
       </c>
-      <c r="H30" s="1">
+      <c r="H31" s="1">
         <v>16.4</v>
       </c>
-      <c r="I30" s="2">
+      <c r="I31" s="2">
         <v>7.6</v>
       </c>
-      <c r="J30">
-        <v>0</v>
-      </c>
-      <c r="K30" s="1">
+      <c r="J31">
+        <v>0</v>
+      </c>
+      <c r="K31" s="1">
         <v>0</v>
       </c>
     </row>
@@ -1551,7 +1586,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:K30"/>
+  <dimension ref="A1:K31"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="2" width="30.7109375" customWidth="1"/>
@@ -1600,34 +1635,34 @@
         <v>11</v>
       </c>
       <c r="B2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C2" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D2">
-        <v>24</v>
+        <v>10</v>
       </c>
       <c r="E2">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="F2">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="G2" s="1">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H2" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="I2" s="2">
-        <v>0</v>
+        <v>9.6</v>
       </c>
       <c r="J2">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="K2" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:11">
@@ -1635,42 +1670,39 @@
         <v>11</v>
       </c>
       <c r="B3" t="s">
-        <v>17</v>
-      </c>
-      <c r="C3" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="D3">
-        <v>28</v>
+        <v>10</v>
       </c>
       <c r="E3">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="F3">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="G3" s="1">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H3" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="I3" s="2">
-        <v>0</v>
+        <v>9.6</v>
       </c>
       <c r="J3">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="K3" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:11">
       <c r="A4" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B4" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C4" t="s">
         <v>23</v>
@@ -1679,92 +1711,95 @@
         <v>24</v>
       </c>
       <c r="E4">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="F4">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="G4" s="1">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H4" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="I4" s="2">
-        <v>0</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="J4">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="K4" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:11">
       <c r="A5" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B5" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C5" t="s">
         <v>24</v>
       </c>
       <c r="D5">
-        <v>37</v>
+        <v>24</v>
       </c>
       <c r="E5">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="F5">
-        <v>37</v>
+        <v>0</v>
       </c>
       <c r="G5" s="1">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H5" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="I5" s="2">
-        <v>0</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="J5">
-        <v>37</v>
+        <v>0</v>
       </c>
       <c r="K5" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:11">
       <c r="A6" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B6" t="s">
         <v>18</v>
       </c>
+      <c r="C6" t="s">
+        <v>25</v>
+      </c>
       <c r="D6">
-        <v>113</v>
+        <v>37</v>
       </c>
       <c r="E6">
-        <v>0</v>
+        <v>37</v>
       </c>
       <c r="F6">
-        <v>113</v>
+        <v>0</v>
       </c>
       <c r="G6" s="1">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H6" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="I6" s="2">
-        <v>0</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="J6">
-        <v>113</v>
+        <v>0</v>
       </c>
       <c r="K6" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:11">
@@ -1774,26 +1809,23 @@
       <c r="B7" t="s">
         <v>19</v>
       </c>
-      <c r="C7" t="s">
-        <v>25</v>
-      </c>
       <c r="D7">
-        <v>34</v>
+        <v>85</v>
       </c>
       <c r="E7">
-        <v>17</v>
+        <v>85</v>
       </c>
       <c r="F7">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="G7" s="1">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="H7" s="1">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="I7" s="2">
-        <v>6.1</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="J7">
         <v>0</v>
@@ -1804,31 +1836,31 @@
     </row>
     <row r="8" spans="1:11">
       <c r="A8" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B8" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C8" t="s">
         <v>26</v>
       </c>
       <c r="D8">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="E8">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="F8">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="G8" s="1">
-        <v>75.8</v>
+        <v>50</v>
       </c>
       <c r="H8" s="1">
-        <v>24.2</v>
+        <v>50</v>
       </c>
       <c r="I8" s="2">
-        <v>7.3</v>
+        <v>6.1</v>
       </c>
       <c r="J8">
         <v>0</v>
@@ -1839,31 +1871,31 @@
     </row>
     <row r="9" spans="1:11">
       <c r="A9" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B9" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C9" t="s">
         <v>27</v>
       </c>
       <c r="D9">
-        <v>23</v>
+        <v>33</v>
       </c>
       <c r="E9">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="F9">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="G9" s="1">
-        <v>43.5</v>
+        <v>75.8</v>
       </c>
       <c r="H9" s="1">
-        <v>56.5</v>
+        <v>24.2</v>
       </c>
       <c r="I9" s="2">
-        <v>5.8</v>
+        <v>7.3</v>
       </c>
       <c r="J9">
         <v>0</v>
@@ -1874,31 +1906,31 @@
     </row>
     <row r="10" spans="1:11">
       <c r="A10" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B10" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C10" t="s">
         <v>28</v>
       </c>
       <c r="D10">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="E10">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="F10">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="G10" s="1">
-        <v>89.5</v>
+        <v>43.5</v>
       </c>
       <c r="H10" s="1">
-        <v>10.5</v>
+        <v>56.5</v>
       </c>
       <c r="I10" s="2">
-        <v>7.4</v>
+        <v>5.8</v>
       </c>
       <c r="J10">
         <v>0</v>
@@ -1909,31 +1941,31 @@
     </row>
     <row r="11" spans="1:11">
       <c r="A11" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B11" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="C11" t="s">
         <v>29</v>
       </c>
       <c r="D11">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="E11">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="F11">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G11" s="1">
-        <v>88</v>
+        <v>89.5</v>
       </c>
       <c r="H11" s="1">
-        <v>12</v>
+        <v>10.5</v>
       </c>
       <c r="I11" s="2">
-        <v>6.9</v>
+        <v>7.4</v>
       </c>
       <c r="J11">
         <v>0</v>
@@ -1944,28 +1976,31 @@
     </row>
     <row r="12" spans="1:11">
       <c r="A12" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B12" t="s">
         <v>18</v>
       </c>
+      <c r="C12" t="s">
+        <v>30</v>
+      </c>
       <c r="D12">
-        <v>134</v>
+        <v>25</v>
       </c>
       <c r="E12">
-        <v>91</v>
+        <v>22</v>
       </c>
       <c r="F12">
-        <v>43</v>
+        <v>3</v>
       </c>
       <c r="G12" s="1">
-        <v>67.90000000000001</v>
+        <v>88</v>
       </c>
       <c r="H12" s="1">
-        <v>32.1</v>
+        <v>12</v>
       </c>
       <c r="I12" s="2">
-        <v>6.7</v>
+        <v>6.9</v>
       </c>
       <c r="J12">
         <v>0</v>
@@ -1979,28 +2014,25 @@
         <v>13</v>
       </c>
       <c r="B13" t="s">
-        <v>17</v>
-      </c>
-      <c r="C13" t="s">
-        <v>30</v>
+        <v>19</v>
       </c>
       <c r="D13">
-        <v>10</v>
+        <v>134</v>
       </c>
       <c r="E13">
-        <v>10</v>
+        <v>91</v>
       </c>
       <c r="F13">
-        <v>0</v>
+        <v>43</v>
       </c>
       <c r="G13" s="1">
-        <v>100</v>
+        <v>67.90000000000001</v>
       </c>
       <c r="H13" s="1">
-        <v>0</v>
+        <v>32.1</v>
       </c>
       <c r="I13" s="2">
-        <v>9.6</v>
+        <v>6.7</v>
       </c>
       <c r="J13">
         <v>0</v>
@@ -2011,28 +2043,31 @@
     </row>
     <row r="14" spans="1:11">
       <c r="A14" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B14" t="s">
         <v>18</v>
       </c>
+      <c r="C14" t="s">
+        <v>31</v>
+      </c>
       <c r="D14">
-        <v>10</v>
+        <v>21</v>
       </c>
       <c r="E14">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="F14">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="G14" s="1">
-        <v>100</v>
+        <v>71.40000000000001</v>
       </c>
       <c r="H14" s="1">
-        <v>0</v>
+        <v>28.6</v>
       </c>
       <c r="I14" s="2">
-        <v>9.6</v>
+        <v>7.2</v>
       </c>
       <c r="J14">
         <v>0</v>
@@ -2046,28 +2081,28 @@
         <v>14</v>
       </c>
       <c r="B15" t="s">
+        <v>18</v>
+      </c>
+      <c r="C15" t="s">
+        <v>32</v>
+      </c>
+      <c r="D15">
+        <v>19</v>
+      </c>
+      <c r="E15">
         <v>17</v>
       </c>
-      <c r="C15" t="s">
-        <v>31</v>
-      </c>
-      <c r="D15">
-        <v>21</v>
-      </c>
-      <c r="E15">
-        <v>15</v>
-      </c>
       <c r="F15">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="G15" s="1">
-        <v>71.40000000000001</v>
+        <v>89.5</v>
       </c>
       <c r="H15" s="1">
-        <v>28.6</v>
+        <v>10.5</v>
       </c>
       <c r="I15" s="2">
-        <v>7.2</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J15">
         <v>0</v>
@@ -2081,28 +2116,28 @@
         <v>14</v>
       </c>
       <c r="B16" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C16" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D16">
+        <v>21</v>
+      </c>
+      <c r="E16">
         <v>19</v>
-      </c>
-      <c r="E16">
-        <v>17</v>
       </c>
       <c r="F16">
         <v>2</v>
       </c>
       <c r="G16" s="1">
-        <v>89.5</v>
+        <v>90.5</v>
       </c>
       <c r="H16" s="1">
-        <v>10.5</v>
+        <v>9.5</v>
       </c>
       <c r="I16" s="2">
-        <v>8.199999999999999</v>
+        <v>8.1</v>
       </c>
       <c r="J16">
         <v>0</v>
@@ -2116,66 +2151,66 @@
         <v>14</v>
       </c>
       <c r="B17" t="s">
-        <v>17</v>
-      </c>
-      <c r="C17" t="s">
-        <v>33</v>
+        <v>19</v>
       </c>
       <c r="D17">
-        <v>21</v>
+        <v>61</v>
       </c>
       <c r="E17">
-        <v>18</v>
+        <v>51</v>
       </c>
       <c r="F17">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="G17" s="1">
-        <v>85.7</v>
+        <v>83.59999999999999</v>
       </c>
       <c r="H17" s="1">
-        <v>14.3</v>
+        <v>16.4</v>
       </c>
       <c r="I17" s="2">
-        <v>8.199999999999999</v>
+        <v>7.8</v>
       </c>
       <c r="J17">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K17" s="1">
-        <v>4.76</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18" spans="1:11">
       <c r="A18" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B18" t="s">
         <v>18</v>
       </c>
+      <c r="C18" t="s">
+        <v>34</v>
+      </c>
       <c r="D18">
-        <v>61</v>
+        <v>28</v>
       </c>
       <c r="E18">
-        <v>50</v>
+        <v>27</v>
       </c>
       <c r="F18">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="G18" s="1">
-        <v>82</v>
+        <v>96.40000000000001</v>
       </c>
       <c r="H18" s="1">
-        <v>18</v>
+        <v>3.6</v>
       </c>
       <c r="I18" s="2">
-        <v>7.9</v>
+        <v>9.6</v>
       </c>
       <c r="J18">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K18" s="1">
-        <v>1.6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19" spans="1:11">
@@ -2185,26 +2220,23 @@
       <c r="B19" t="s">
         <v>19</v>
       </c>
-      <c r="C19" t="s">
-        <v>34</v>
-      </c>
       <c r="D19">
-        <v>40</v>
+        <v>28</v>
       </c>
       <c r="E19">
-        <v>36</v>
+        <v>27</v>
       </c>
       <c r="F19">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G19" s="1">
-        <v>90</v>
+        <v>96.40000000000001</v>
       </c>
       <c r="H19" s="1">
-        <v>10</v>
+        <v>3.6</v>
       </c>
       <c r="I19" s="2">
-        <v>8.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="J19">
         <v>0</v>
@@ -2215,31 +2247,31 @@
     </row>
     <row r="20" spans="1:11">
       <c r="A20" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B20" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C20" t="s">
         <v>35</v>
       </c>
       <c r="D20">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E20">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="F20">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="G20" s="1">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="H20" s="1">
-        <v>22</v>
+        <v>10</v>
       </c>
       <c r="I20" s="2">
-        <v>7.1</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J20">
         <v>0</v>
@@ -2250,31 +2282,31 @@
     </row>
     <row r="21" spans="1:11">
       <c r="A21" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B21" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C21" t="s">
         <v>36</v>
       </c>
       <c r="D21">
-        <v>48</v>
+        <v>41</v>
       </c>
       <c r="E21">
-        <v>44</v>
+        <v>32</v>
       </c>
       <c r="F21">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="G21" s="1">
-        <v>91.7</v>
+        <v>78</v>
       </c>
       <c r="H21" s="1">
-        <v>8.300000000000001</v>
+        <v>22</v>
       </c>
       <c r="I21" s="2">
-        <v>7.6</v>
+        <v>7.1</v>
       </c>
       <c r="J21">
         <v>0</v>
@@ -2285,31 +2317,31 @@
     </row>
     <row r="22" spans="1:11">
       <c r="A22" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B22" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C22" t="s">
         <v>37</v>
       </c>
       <c r="D22">
-        <v>36</v>
+        <v>48</v>
       </c>
       <c r="E22">
-        <v>35</v>
+        <v>44</v>
       </c>
       <c r="F22">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G22" s="1">
-        <v>97.2</v>
+        <v>91.7</v>
       </c>
       <c r="H22" s="1">
-        <v>2.8</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="I22" s="2">
-        <v>8.300000000000001</v>
+        <v>7.6</v>
       </c>
       <c r="J22">
         <v>0</v>
@@ -2320,31 +2352,31 @@
     </row>
     <row r="23" spans="1:11">
       <c r="A23" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B23" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C23" t="s">
         <v>38</v>
       </c>
       <c r="D23">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="E23">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="F23">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="G23" s="1">
-        <v>81.09999999999999</v>
+        <v>97.2</v>
       </c>
       <c r="H23" s="1">
-        <v>18.9</v>
+        <v>2.8</v>
       </c>
       <c r="I23" s="2">
-        <v>7.3</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="J23">
         <v>0</v>
@@ -2355,31 +2387,31 @@
     </row>
     <row r="24" spans="1:11">
       <c r="A24" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B24" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C24" t="s">
         <v>39</v>
       </c>
       <c r="D24">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="E24">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F24">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="G24" s="1">
-        <v>87.90000000000001</v>
+        <v>81.09999999999999</v>
       </c>
       <c r="H24" s="1">
-        <v>12.1</v>
+        <v>18.9</v>
       </c>
       <c r="I24" s="2">
-        <v>8.1</v>
+        <v>7.3</v>
       </c>
       <c r="J24">
         <v>0</v>
@@ -2390,31 +2422,31 @@
     </row>
     <row r="25" spans="1:11">
       <c r="A25" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B25" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="C25" t="s">
         <v>40</v>
       </c>
       <c r="D25">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="E25">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="F25">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G25" s="1">
-        <v>94.40000000000001</v>
+        <v>87.90000000000001</v>
       </c>
       <c r="H25" s="1">
-        <v>5.6</v>
+        <v>12.1</v>
       </c>
       <c r="I25" s="2">
-        <v>8.300000000000001</v>
+        <v>8.1</v>
       </c>
       <c r="J25">
         <v>0</v>
@@ -2425,31 +2457,31 @@
     </row>
     <row r="26" spans="1:11">
       <c r="A26" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B26" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C26" t="s">
         <v>41</v>
       </c>
       <c r="D26">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E26">
         <v>34</v>
       </c>
       <c r="F26">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G26" s="1">
-        <v>97.09999999999999</v>
+        <v>94.40000000000001</v>
       </c>
       <c r="H26" s="1">
-        <v>2.9</v>
+        <v>5.6</v>
       </c>
       <c r="I26" s="2">
-        <v>8.6</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="J26">
         <v>0</v>
@@ -2460,28 +2492,31 @@
     </row>
     <row r="27" spans="1:11">
       <c r="A27" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B27" t="s">
         <v>18</v>
       </c>
+      <c r="C27" t="s">
+        <v>42</v>
+      </c>
       <c r="D27">
-        <v>306</v>
+        <v>35</v>
       </c>
       <c r="E27">
-        <v>274</v>
+        <v>34</v>
       </c>
       <c r="F27">
-        <v>32</v>
+        <v>1</v>
       </c>
       <c r="G27" s="1">
-        <v>89.5</v>
+        <v>97.09999999999999</v>
       </c>
       <c r="H27" s="1">
-        <v>10.5</v>
+        <v>2.9</v>
       </c>
       <c r="I27" s="2">
-        <v>7.9</v>
+        <v>8.6</v>
       </c>
       <c r="J27">
         <v>0</v>
@@ -2497,26 +2532,23 @@
       <c r="B28" t="s">
         <v>19</v>
       </c>
-      <c r="C28" t="s">
-        <v>42</v>
-      </c>
       <c r="D28">
-        <v>40</v>
+        <v>306</v>
       </c>
       <c r="E28">
-        <v>18</v>
+        <v>274</v>
       </c>
       <c r="F28">
-        <v>22</v>
+        <v>32</v>
       </c>
       <c r="G28" s="1">
-        <v>45</v>
+        <v>89.5</v>
       </c>
       <c r="H28" s="1">
-        <v>55</v>
+        <v>10.5</v>
       </c>
       <c r="I28" s="2">
-        <v>5.7</v>
+        <v>7.9</v>
       </c>
       <c r="J28">
         <v>0</v>
@@ -2527,10 +2559,13 @@
     </row>
     <row r="29" spans="1:11">
       <c r="A29" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B29" t="s">
-        <v>18</v>
+        <v>20</v>
+      </c>
+      <c r="C29" t="s">
+        <v>43</v>
       </c>
       <c r="D29">
         <v>40</v>
@@ -2558,32 +2593,64 @@
       </c>
     </row>
     <row r="30" spans="1:11">
+      <c r="A30" t="s">
+        <v>17</v>
+      </c>
       <c r="B30" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D30">
+        <v>40</v>
+      </c>
+      <c r="E30">
+        <v>18</v>
+      </c>
+      <c r="F30">
+        <v>22</v>
+      </c>
+      <c r="G30" s="1">
+        <v>45</v>
+      </c>
+      <c r="H30" s="1">
+        <v>55</v>
+      </c>
+      <c r="I30" s="2">
+        <v>5.7</v>
+      </c>
+      <c r="J30">
+        <v>0</v>
+      </c>
+      <c r="K30" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="1:11">
+      <c r="B31" t="s">
+        <v>21</v>
+      </c>
+      <c r="D31">
         <v>664</v>
       </c>
-      <c r="E30">
-        <v>443</v>
-      </c>
-      <c r="F30">
-        <v>221</v>
-      </c>
-      <c r="G30" s="1">
-        <v>66.7</v>
-      </c>
-      <c r="H30" s="1">
-        <v>33.3</v>
-      </c>
-      <c r="I30" s="2">
-        <v>6.2</v>
-      </c>
-      <c r="J30">
-        <v>114</v>
-      </c>
-      <c r="K30" s="1">
-        <v>17.2</v>
+      <c r="E31">
+        <v>556</v>
+      </c>
+      <c r="F31">
+        <v>108</v>
+      </c>
+      <c r="G31" s="1">
+        <v>83.7</v>
+      </c>
+      <c r="H31" s="1">
+        <v>16.3</v>
+      </c>
+      <c r="I31" s="2">
+        <v>7.9</v>
+      </c>
+      <c r="J31">
+        <v>0</v>
+      </c>
+      <c r="K31" s="1">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -2593,7 +2660,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:K30"/>
+  <dimension ref="A1:K31"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="2" width="30.7109375" customWidth="1"/>
@@ -2642,28 +2709,28 @@
         <v>11</v>
       </c>
       <c r="B2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C2" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D2">
-        <v>24</v>
+        <v>10</v>
       </c>
       <c r="E2">
-        <v>23</v>
+        <v>10</v>
       </c>
       <c r="F2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G2" s="1">
-        <v>95.8</v>
+        <v>100</v>
       </c>
       <c r="H2" s="1">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="I2" s="2">
-        <v>8.300000000000001</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="J2">
         <v>0</v>
@@ -2677,28 +2744,25 @@
         <v>11</v>
       </c>
       <c r="B3" t="s">
-        <v>17</v>
-      </c>
-      <c r="C3" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="D3">
-        <v>28</v>
+        <v>10</v>
       </c>
       <c r="E3">
-        <v>27</v>
+        <v>10</v>
       </c>
       <c r="F3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G3" s="1">
-        <v>96.40000000000001</v>
+        <v>100</v>
       </c>
       <c r="H3" s="1">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="I3" s="2">
-        <v>8.9</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="J3">
         <v>0</v>
@@ -2709,10 +2773,10 @@
     </row>
     <row r="4" spans="1:11">
       <c r="A4" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B4" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C4" t="s">
         <v>23</v>
@@ -2721,19 +2785,19 @@
         <v>24</v>
       </c>
       <c r="E4">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G4" s="1">
-        <v>95.8</v>
+        <v>100</v>
       </c>
       <c r="H4" s="1">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="I4" s="2">
-        <v>8.4</v>
+        <v>9.1</v>
       </c>
       <c r="J4">
         <v>0</v>
@@ -2744,31 +2808,31 @@
     </row>
     <row r="5" spans="1:11">
       <c r="A5" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B5" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C5" t="s">
         <v>24</v>
       </c>
       <c r="D5">
-        <v>37</v>
+        <v>24</v>
       </c>
       <c r="E5">
-        <v>35</v>
+        <v>24</v>
       </c>
       <c r="F5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G5" s="1">
-        <v>94.59999999999999</v>
+        <v>100</v>
       </c>
       <c r="H5" s="1">
-        <v>5.4</v>
+        <v>0</v>
       </c>
       <c r="I5" s="2">
-        <v>8.300000000000001</v>
+        <v>9</v>
       </c>
       <c r="J5">
         <v>0</v>
@@ -2779,28 +2843,31 @@
     </row>
     <row r="6" spans="1:11">
       <c r="A6" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B6" t="s">
         <v>18</v>
       </c>
+      <c r="C6" t="s">
+        <v>25</v>
+      </c>
       <c r="D6">
-        <v>113</v>
+        <v>37</v>
       </c>
       <c r="E6">
-        <v>108</v>
+        <v>37</v>
       </c>
       <c r="F6">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="G6" s="1">
-        <v>95.59999999999999</v>
+        <v>100</v>
       </c>
       <c r="H6" s="1">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="I6" s="2">
-        <v>8.5</v>
+        <v>9.1</v>
       </c>
       <c r="J6">
         <v>0</v>
@@ -2816,26 +2883,23 @@
       <c r="B7" t="s">
         <v>19</v>
       </c>
-      <c r="C7" t="s">
-        <v>25</v>
-      </c>
       <c r="D7">
-        <v>34</v>
+        <v>85</v>
       </c>
       <c r="E7">
-        <v>17</v>
+        <v>85</v>
       </c>
       <c r="F7">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="G7" s="1">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="H7" s="1">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="I7" s="2">
-        <v>6.1</v>
+        <v>9.1</v>
       </c>
       <c r="J7">
         <v>0</v>
@@ -2846,31 +2910,31 @@
     </row>
     <row r="8" spans="1:11">
       <c r="A8" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B8" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C8" t="s">
         <v>26</v>
       </c>
       <c r="D8">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="E8">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="F8">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="G8" s="1">
-        <v>75.8</v>
+        <v>50</v>
       </c>
       <c r="H8" s="1">
-        <v>24.2</v>
+        <v>50</v>
       </c>
       <c r="I8" s="2">
-        <v>6.9</v>
+        <v>6.1</v>
       </c>
       <c r="J8">
         <v>0</v>
@@ -2881,31 +2945,31 @@
     </row>
     <row r="9" spans="1:11">
       <c r="A9" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B9" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C9" t="s">
         <v>27</v>
       </c>
       <c r="D9">
-        <v>23</v>
+        <v>33</v>
       </c>
       <c r="E9">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="F9">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="G9" s="1">
-        <v>43.5</v>
+        <v>75.8</v>
       </c>
       <c r="H9" s="1">
-        <v>56.5</v>
+        <v>24.2</v>
       </c>
       <c r="I9" s="2">
-        <v>5.9</v>
+        <v>6.9</v>
       </c>
       <c r="J9">
         <v>0</v>
@@ -2916,31 +2980,31 @@
     </row>
     <row r="10" spans="1:11">
       <c r="A10" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B10" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C10" t="s">
         <v>28</v>
       </c>
       <c r="D10">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="E10">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="F10">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="G10" s="1">
-        <v>89.5</v>
+        <v>43.5</v>
       </c>
       <c r="H10" s="1">
-        <v>10.5</v>
+        <v>56.5</v>
       </c>
       <c r="I10" s="2">
-        <v>7.3</v>
+        <v>5.9</v>
       </c>
       <c r="J10">
         <v>0</v>
@@ -2951,28 +3015,28 @@
     </row>
     <row r="11" spans="1:11">
       <c r="A11" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B11" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="C11" t="s">
         <v>29</v>
       </c>
       <c r="D11">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="E11">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="F11">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G11" s="1">
-        <v>88</v>
+        <v>89.5</v>
       </c>
       <c r="H11" s="1">
-        <v>12</v>
+        <v>10.5</v>
       </c>
       <c r="I11" s="2">
         <v>7.3</v>
@@ -2986,28 +3050,31 @@
     </row>
     <row r="12" spans="1:11">
       <c r="A12" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B12" t="s">
         <v>18</v>
       </c>
+      <c r="C12" t="s">
+        <v>30</v>
+      </c>
       <c r="D12">
-        <v>134</v>
+        <v>25</v>
       </c>
       <c r="E12">
-        <v>91</v>
+        <v>22</v>
       </c>
       <c r="F12">
-        <v>43</v>
+        <v>3</v>
       </c>
       <c r="G12" s="1">
-        <v>67.90000000000001</v>
+        <v>88</v>
       </c>
       <c r="H12" s="1">
-        <v>32.1</v>
+        <v>12</v>
       </c>
       <c r="I12" s="2">
-        <v>6.7</v>
+        <v>7.3</v>
       </c>
       <c r="J12">
         <v>0</v>
@@ -3021,28 +3088,25 @@
         <v>13</v>
       </c>
       <c r="B13" t="s">
-        <v>17</v>
-      </c>
-      <c r="C13" t="s">
-        <v>30</v>
+        <v>19</v>
       </c>
       <c r="D13">
-        <v>10</v>
+        <v>134</v>
       </c>
       <c r="E13">
-        <v>10</v>
+        <v>91</v>
       </c>
       <c r="F13">
-        <v>0</v>
+        <v>43</v>
       </c>
       <c r="G13" s="1">
-        <v>100</v>
+        <v>67.90000000000001</v>
       </c>
       <c r="H13" s="1">
-        <v>0</v>
+        <v>32.1</v>
       </c>
       <c r="I13" s="2">
-        <v>9.300000000000001</v>
+        <v>6.7</v>
       </c>
       <c r="J13">
         <v>0</v>
@@ -3053,28 +3117,31 @@
     </row>
     <row r="14" spans="1:11">
       <c r="A14" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B14" t="s">
         <v>18</v>
       </c>
+      <c r="C14" t="s">
+        <v>31</v>
+      </c>
       <c r="D14">
-        <v>10</v>
+        <v>21</v>
       </c>
       <c r="E14">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="F14">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="G14" s="1">
-        <v>100</v>
+        <v>71.40000000000001</v>
       </c>
       <c r="H14" s="1">
-        <v>0</v>
+        <v>28.6</v>
       </c>
       <c r="I14" s="2">
-        <v>9.300000000000001</v>
+        <v>6.9</v>
       </c>
       <c r="J14">
         <v>0</v>
@@ -3088,28 +3155,28 @@
         <v>14</v>
       </c>
       <c r="B15" t="s">
+        <v>18</v>
+      </c>
+      <c r="C15" t="s">
+        <v>32</v>
+      </c>
+      <c r="D15">
+        <v>19</v>
+      </c>
+      <c r="E15">
         <v>17</v>
       </c>
-      <c r="C15" t="s">
-        <v>31</v>
-      </c>
-      <c r="D15">
-        <v>21</v>
-      </c>
-      <c r="E15">
-        <v>15</v>
-      </c>
       <c r="F15">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="G15" s="1">
-        <v>71.40000000000001</v>
+        <v>89.5</v>
       </c>
       <c r="H15" s="1">
-        <v>28.6</v>
+        <v>10.5</v>
       </c>
       <c r="I15" s="2">
-        <v>6.9</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="J15">
         <v>0</v>
@@ -3123,28 +3190,28 @@
         <v>14</v>
       </c>
       <c r="B16" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C16" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D16">
+        <v>21</v>
+      </c>
+      <c r="E16">
         <v>19</v>
-      </c>
-      <c r="E16">
-        <v>17</v>
       </c>
       <c r="F16">
         <v>2</v>
       </c>
       <c r="G16" s="1">
-        <v>89.5</v>
+        <v>90.5</v>
       </c>
       <c r="H16" s="1">
-        <v>10.5</v>
+        <v>9.5</v>
       </c>
       <c r="I16" s="2">
-        <v>8.300000000000001</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J16">
         <v>0</v>
@@ -3158,28 +3225,25 @@
         <v>14</v>
       </c>
       <c r="B17" t="s">
-        <v>17</v>
-      </c>
-      <c r="C17" t="s">
-        <v>33</v>
+        <v>19</v>
       </c>
       <c r="D17">
-        <v>21</v>
+        <v>61</v>
       </c>
       <c r="E17">
-        <v>19</v>
+        <v>51</v>
       </c>
       <c r="F17">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="G17" s="1">
-        <v>90.5</v>
+        <v>83.59999999999999</v>
       </c>
       <c r="H17" s="1">
-        <v>9.5</v>
+        <v>16.4</v>
       </c>
       <c r="I17" s="2">
-        <v>8.199999999999999</v>
+        <v>7.8</v>
       </c>
       <c r="J17">
         <v>0</v>
@@ -3190,28 +3254,31 @@
     </row>
     <row r="18" spans="1:11">
       <c r="A18" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B18" t="s">
         <v>18</v>
       </c>
+      <c r="C18" t="s">
+        <v>34</v>
+      </c>
       <c r="D18">
-        <v>61</v>
+        <v>28</v>
       </c>
       <c r="E18">
-        <v>51</v>
+        <v>27</v>
       </c>
       <c r="F18">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="G18" s="1">
-        <v>83.59999999999999</v>
+        <v>96.40000000000001</v>
       </c>
       <c r="H18" s="1">
-        <v>16.4</v>
+        <v>3.6</v>
       </c>
       <c r="I18" s="2">
-        <v>7.8</v>
+        <v>9.4</v>
       </c>
       <c r="J18">
         <v>0</v>
@@ -3227,26 +3294,23 @@
       <c r="B19" t="s">
         <v>19</v>
       </c>
-      <c r="C19" t="s">
-        <v>34</v>
-      </c>
       <c r="D19">
-        <v>40</v>
+        <v>28</v>
       </c>
       <c r="E19">
-        <v>36</v>
+        <v>27</v>
       </c>
       <c r="F19">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G19" s="1">
-        <v>90</v>
+        <v>96.40000000000001</v>
       </c>
       <c r="H19" s="1">
-        <v>10</v>
+        <v>3.6</v>
       </c>
       <c r="I19" s="2">
-        <v>8.5</v>
+        <v>9.4</v>
       </c>
       <c r="J19">
         <v>0</v>
@@ -3257,31 +3321,31 @@
     </row>
     <row r="20" spans="1:11">
       <c r="A20" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B20" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C20" t="s">
         <v>35</v>
       </c>
       <c r="D20">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E20">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="F20">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="G20" s="1">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="H20" s="1">
-        <v>22</v>
+        <v>10</v>
       </c>
       <c r="I20" s="2">
-        <v>7.4</v>
+        <v>8.5</v>
       </c>
       <c r="J20">
         <v>0</v>
@@ -3292,31 +3356,31 @@
     </row>
     <row r="21" spans="1:11">
       <c r="A21" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B21" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C21" t="s">
         <v>36</v>
       </c>
       <c r="D21">
-        <v>48</v>
+        <v>41</v>
       </c>
       <c r="E21">
-        <v>44</v>
+        <v>32</v>
       </c>
       <c r="F21">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="G21" s="1">
-        <v>91.7</v>
+        <v>78</v>
       </c>
       <c r="H21" s="1">
-        <v>8.300000000000001</v>
+        <v>22</v>
       </c>
       <c r="I21" s="2">
-        <v>8.1</v>
+        <v>7.4</v>
       </c>
       <c r="J21">
         <v>0</v>
@@ -3327,31 +3391,31 @@
     </row>
     <row r="22" spans="1:11">
       <c r="A22" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B22" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C22" t="s">
         <v>37</v>
       </c>
       <c r="D22">
-        <v>36</v>
+        <v>48</v>
       </c>
       <c r="E22">
-        <v>35</v>
+        <v>44</v>
       </c>
       <c r="F22">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G22" s="1">
-        <v>97.2</v>
+        <v>91.7</v>
       </c>
       <c r="H22" s="1">
-        <v>2.8</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="I22" s="2">
-        <v>8.699999999999999</v>
+        <v>8.1</v>
       </c>
       <c r="J22">
         <v>0</v>
@@ -3362,31 +3426,31 @@
     </row>
     <row r="23" spans="1:11">
       <c r="A23" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B23" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C23" t="s">
         <v>38</v>
       </c>
       <c r="D23">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="E23">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="F23">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="G23" s="1">
-        <v>81.09999999999999</v>
+        <v>97.2</v>
       </c>
       <c r="H23" s="1">
-        <v>18.9</v>
+        <v>2.8</v>
       </c>
       <c r="I23" s="2">
-        <v>7.8</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="J23">
         <v>0</v>
@@ -3397,31 +3461,31 @@
     </row>
     <row r="24" spans="1:11">
       <c r="A24" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B24" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C24" t="s">
         <v>39</v>
       </c>
       <c r="D24">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="E24">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F24">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="G24" s="1">
-        <v>87.90000000000001</v>
+        <v>81.09999999999999</v>
       </c>
       <c r="H24" s="1">
-        <v>12.1</v>
+        <v>18.9</v>
       </c>
       <c r="I24" s="2">
-        <v>8.1</v>
+        <v>7.8</v>
       </c>
       <c r="J24">
         <v>0</v>
@@ -3432,31 +3496,31 @@
     </row>
     <row r="25" spans="1:11">
       <c r="A25" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B25" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="C25" t="s">
         <v>40</v>
       </c>
       <c r="D25">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="E25">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="F25">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G25" s="1">
-        <v>94.40000000000001</v>
+        <v>87.90000000000001</v>
       </c>
       <c r="H25" s="1">
-        <v>5.6</v>
+        <v>12.1</v>
       </c>
       <c r="I25" s="2">
-        <v>8.6</v>
+        <v>8.1</v>
       </c>
       <c r="J25">
         <v>0</v>
@@ -3467,31 +3531,31 @@
     </row>
     <row r="26" spans="1:11">
       <c r="A26" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B26" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C26" t="s">
         <v>41</v>
       </c>
       <c r="D26">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E26">
         <v>34</v>
       </c>
       <c r="F26">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G26" s="1">
-        <v>97.09999999999999</v>
+        <v>94.40000000000001</v>
       </c>
       <c r="H26" s="1">
-        <v>2.9</v>
+        <v>5.6</v>
       </c>
       <c r="I26" s="2">
-        <v>8.9</v>
+        <v>8.6</v>
       </c>
       <c r="J26">
         <v>0</v>
@@ -3502,28 +3566,31 @@
     </row>
     <row r="27" spans="1:11">
       <c r="A27" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B27" t="s">
         <v>18</v>
       </c>
+      <c r="C27" t="s">
+        <v>42</v>
+      </c>
       <c r="D27">
-        <v>306</v>
+        <v>35</v>
       </c>
       <c r="E27">
-        <v>274</v>
+        <v>34</v>
       </c>
       <c r="F27">
-        <v>32</v>
+        <v>1</v>
       </c>
       <c r="G27" s="1">
-        <v>89.5</v>
+        <v>97.09999999999999</v>
       </c>
       <c r="H27" s="1">
-        <v>10.5</v>
+        <v>2.9</v>
       </c>
       <c r="I27" s="2">
-        <v>8.300000000000001</v>
+        <v>8.9</v>
       </c>
       <c r="J27">
         <v>0</v>
@@ -3539,26 +3606,23 @@
       <c r="B28" t="s">
         <v>19</v>
       </c>
-      <c r="C28" t="s">
-        <v>42</v>
-      </c>
       <c r="D28">
-        <v>40</v>
+        <v>306</v>
       </c>
       <c r="E28">
-        <v>18</v>
+        <v>274</v>
       </c>
       <c r="F28">
-        <v>22</v>
+        <v>32</v>
       </c>
       <c r="G28" s="1">
-        <v>45</v>
+        <v>89.5</v>
       </c>
       <c r="H28" s="1">
-        <v>55</v>
+        <v>10.5</v>
       </c>
       <c r="I28" s="2">
-        <v>5.8</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="J28">
         <v>0</v>
@@ -3569,10 +3633,13 @@
     </row>
     <row r="29" spans="1:11">
       <c r="A29" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B29" t="s">
-        <v>18</v>
+        <v>20</v>
+      </c>
+      <c r="C29" t="s">
+        <v>43</v>
       </c>
       <c r="D29">
         <v>40</v>
@@ -3600,31 +3667,63 @@
       </c>
     </row>
     <row r="30" spans="1:11">
+      <c r="A30" t="s">
+        <v>17</v>
+      </c>
       <c r="B30" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D30">
+        <v>40</v>
+      </c>
+      <c r="E30">
+        <v>18</v>
+      </c>
+      <c r="F30">
+        <v>22</v>
+      </c>
+      <c r="G30" s="1">
+        <v>45</v>
+      </c>
+      <c r="H30" s="1">
+        <v>55</v>
+      </c>
+      <c r="I30" s="2">
+        <v>5.8</v>
+      </c>
+      <c r="J30">
+        <v>0</v>
+      </c>
+      <c r="K30" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="1:11">
+      <c r="B31" t="s">
+        <v>21</v>
+      </c>
+      <c r="D31">
         <v>664</v>
       </c>
-      <c r="E30">
-        <v>552</v>
-      </c>
-      <c r="F30">
-        <v>112</v>
-      </c>
-      <c r="G30" s="1">
-        <v>83.09999999999999</v>
-      </c>
-      <c r="H30" s="1">
-        <v>16.9</v>
-      </c>
-      <c r="I30" s="2">
-        <v>7.8</v>
-      </c>
-      <c r="J30">
-        <v>0</v>
-      </c>
-      <c r="K30" s="1">
+      <c r="E31">
+        <v>556</v>
+      </c>
+      <c r="F31">
+        <v>108</v>
+      </c>
+      <c r="G31" s="1">
+        <v>83.7</v>
+      </c>
+      <c r="H31" s="1">
+        <v>16.3</v>
+      </c>
+      <c r="I31" s="2">
+        <v>7.9</v>
+      </c>
+      <c r="J31">
+        <v>0</v>
+      </c>
+      <c r="K31" s="1">
         <v>0</v>
       </c>
     </row>

--- a/academias/Humanidades - Estadisticos 20241.xlsx
+++ b/academias/Humanidades - Estadisticos 20241.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="276" uniqueCount="44">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="270" uniqueCount="43">
   <si>
     <t>Docente</t>
   </si>
@@ -54,9 +54,6 @@
     <t>Breniz Camarillo Lysette</t>
   </si>
   <si>
-    <t>Castro Vasquez Julieta</t>
-  </si>
-  <si>
     <t>Gaspar Velazco Juan Francisco</t>
   </si>
   <si>
@@ -87,40 +84,40 @@
     <t>3ASV</t>
   </si>
   <si>
+    <t>1BV</t>
+  </si>
+  <si>
+    <t>1CV</t>
+  </si>
+  <si>
+    <t>1DV</t>
+  </si>
+  <si>
+    <t>1EV</t>
+  </si>
+  <si>
+    <t>3ALCV</t>
+  </si>
+  <si>
+    <t>3AEV</t>
+  </si>
+  <si>
+    <t>3APV</t>
+  </si>
+  <si>
+    <t>3ARHV</t>
+  </si>
+  <si>
     <t>3AEM</t>
   </si>
   <si>
+    <t>3APM</t>
+  </si>
+  <si>
     <t>3BEM</t>
   </si>
   <si>
     <t>3BLCM</t>
-  </si>
-  <si>
-    <t>1BV</t>
-  </si>
-  <si>
-    <t>1CV</t>
-  </si>
-  <si>
-    <t>1DV</t>
-  </si>
-  <si>
-    <t>1EV</t>
-  </si>
-  <si>
-    <t>3ALCV</t>
-  </si>
-  <si>
-    <t>3AEV</t>
-  </si>
-  <si>
-    <t>3APV</t>
-  </si>
-  <si>
-    <t>3ARHV</t>
-  </si>
-  <si>
-    <t>3APM</t>
   </si>
   <si>
     <t>1AM</t>
@@ -511,7 +508,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:K31"/>
+  <dimension ref="A1:K30"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -561,10 +558,10 @@
         <v>11</v>
       </c>
       <c r="B2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C2" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D2">
         <v>10</v>
@@ -596,7 +593,7 @@
         <v>11</v>
       </c>
       <c r="B3" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D3">
         <v>10</v>
@@ -628,28 +625,28 @@
         <v>12</v>
       </c>
       <c r="B4" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D4">
-        <v>24</v>
+        <v>34</v>
       </c>
       <c r="E4">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="F4">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="G4" s="1">
-        <v>95.8</v>
+        <v>58.8</v>
       </c>
       <c r="H4" s="1">
-        <v>4.2</v>
+        <v>41.2</v>
       </c>
       <c r="I4" s="2">
-        <v>8.300000000000001</v>
+        <v>5.4</v>
       </c>
       <c r="J4">
         <v>0</v>
@@ -663,28 +660,28 @@
         <v>12</v>
       </c>
       <c r="B5" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C5" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D5">
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="E5">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="F5">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="G5" s="1">
-        <v>95.8</v>
+        <v>81.8</v>
       </c>
       <c r="H5" s="1">
-        <v>4.2</v>
+        <v>18.2</v>
       </c>
       <c r="I5" s="2">
-        <v>8.4</v>
+        <v>6</v>
       </c>
       <c r="J5">
         <v>0</v>
@@ -698,28 +695,28 @@
         <v>12</v>
       </c>
       <c r="B6" t="s">
+        <v>19</v>
+      </c>
+      <c r="C6" t="s">
+        <v>24</v>
+      </c>
+      <c r="D6">
+        <v>23</v>
+      </c>
+      <c r="E6">
         <v>18</v>
       </c>
-      <c r="C6" t="s">
-        <v>25</v>
-      </c>
-      <c r="D6">
-        <v>37</v>
-      </c>
-      <c r="E6">
-        <v>35</v>
-      </c>
       <c r="F6">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="G6" s="1">
-        <v>94.59999999999999</v>
+        <v>78.3</v>
       </c>
       <c r="H6" s="1">
-        <v>5.4</v>
+        <v>21.7</v>
       </c>
       <c r="I6" s="2">
-        <v>8.300000000000001</v>
+        <v>6</v>
       </c>
       <c r="J6">
         <v>0</v>
@@ -735,23 +732,26 @@
       <c r="B7" t="s">
         <v>19</v>
       </c>
+      <c r="C7" t="s">
+        <v>25</v>
+      </c>
       <c r="D7">
-        <v>85</v>
+        <v>19</v>
       </c>
       <c r="E7">
-        <v>81</v>
+        <v>17</v>
       </c>
       <c r="F7">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G7" s="1">
-        <v>95.3</v>
+        <v>89.5</v>
       </c>
       <c r="H7" s="1">
-        <v>4.7</v>
+        <v>10.5</v>
       </c>
       <c r="I7" s="2">
-        <v>8.300000000000001</v>
+        <v>6.7</v>
       </c>
       <c r="J7">
         <v>0</v>
@@ -762,31 +762,31 @@
     </row>
     <row r="8" spans="1:11">
       <c r="A8" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B8" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="C8" t="s">
         <v>26</v>
       </c>
       <c r="D8">
-        <v>34</v>
+        <v>25</v>
       </c>
       <c r="E8">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="F8">
-        <v>14</v>
+        <v>3</v>
       </c>
       <c r="G8" s="1">
-        <v>58.8</v>
+        <v>88</v>
       </c>
       <c r="H8" s="1">
-        <v>41.2</v>
+        <v>12</v>
       </c>
       <c r="I8" s="2">
-        <v>5.4</v>
+        <v>7</v>
       </c>
       <c r="J8">
         <v>0</v>
@@ -797,31 +797,28 @@
     </row>
     <row r="9" spans="1:11">
       <c r="A9" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B9" t="s">
-        <v>20</v>
-      </c>
-      <c r="C9" t="s">
-        <v>27</v>
+        <v>18</v>
       </c>
       <c r="D9">
-        <v>33</v>
+        <v>134</v>
       </c>
       <c r="E9">
-        <v>27</v>
+        <v>104</v>
       </c>
       <c r="F9">
-        <v>6</v>
+        <v>30</v>
       </c>
       <c r="G9" s="1">
-        <v>81.8</v>
+        <v>77.59999999999999</v>
       </c>
       <c r="H9" s="1">
-        <v>18.2</v>
+        <v>22.4</v>
       </c>
       <c r="I9" s="2">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="J9">
         <v>0</v>
@@ -835,25 +832,25 @@
         <v>13</v>
       </c>
       <c r="B10" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="C10" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D10">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="E10">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="F10">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G10" s="1">
-        <v>78.3</v>
+        <v>71.40000000000001</v>
       </c>
       <c r="H10" s="1">
-        <v>21.7</v>
+        <v>28.6</v>
       </c>
       <c r="I10" s="2">
         <v>6</v>
@@ -870,10 +867,10 @@
         <v>13</v>
       </c>
       <c r="B11" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="C11" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D11">
         <v>19</v>
@@ -891,7 +888,7 @@
         <v>10.5</v>
       </c>
       <c r="I11" s="2">
-        <v>6.7</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J11">
         <v>0</v>
@@ -905,28 +902,28 @@
         <v>13</v>
       </c>
       <c r="B12" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C12" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D12">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="E12">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="F12">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G12" s="1">
-        <v>88</v>
+        <v>90.5</v>
       </c>
       <c r="H12" s="1">
-        <v>12</v>
+        <v>9.5</v>
       </c>
       <c r="I12" s="2">
-        <v>7</v>
+        <v>7.9</v>
       </c>
       <c r="J12">
         <v>0</v>
@@ -940,25 +937,25 @@
         <v>13</v>
       </c>
       <c r="B13" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D13">
-        <v>134</v>
+        <v>61</v>
       </c>
       <c r="E13">
-        <v>104</v>
+        <v>51</v>
       </c>
       <c r="F13">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="G13" s="1">
-        <v>77.59999999999999</v>
+        <v>83.59999999999999</v>
       </c>
       <c r="H13" s="1">
-        <v>22.4</v>
+        <v>16.4</v>
       </c>
       <c r="I13" s="2">
-        <v>6.2</v>
+        <v>7.4</v>
       </c>
       <c r="J13">
         <v>0</v>
@@ -972,28 +969,28 @@
         <v>14</v>
       </c>
       <c r="B14" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C14" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D14">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="E14">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="F14">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="G14" s="1">
-        <v>71.40000000000001</v>
+        <v>95.8</v>
       </c>
       <c r="H14" s="1">
-        <v>28.6</v>
+        <v>4.2</v>
       </c>
       <c r="I14" s="2">
-        <v>6</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="J14">
         <v>0</v>
@@ -1007,28 +1004,28 @@
         <v>14</v>
       </c>
       <c r="B15" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C15" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D15">
-        <v>19</v>
+        <v>28</v>
       </c>
       <c r="E15">
-        <v>17</v>
+        <v>27</v>
       </c>
       <c r="F15">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G15" s="1">
-        <v>89.5</v>
+        <v>96.40000000000001</v>
       </c>
       <c r="H15" s="1">
-        <v>10.5</v>
+        <v>3.6</v>
       </c>
       <c r="I15" s="2">
-        <v>8.199999999999999</v>
+        <v>8.9</v>
       </c>
       <c r="J15">
         <v>0</v>
@@ -1042,28 +1039,28 @@
         <v>14</v>
       </c>
       <c r="B16" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C16" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D16">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="E16">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="F16">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G16" s="1">
-        <v>90.5</v>
+        <v>95.8</v>
       </c>
       <c r="H16" s="1">
-        <v>9.5</v>
+        <v>4.2</v>
       </c>
       <c r="I16" s="2">
-        <v>7.9</v>
+        <v>8.4</v>
       </c>
       <c r="J16">
         <v>0</v>
@@ -1077,25 +1074,28 @@
         <v>14</v>
       </c>
       <c r="B17" t="s">
-        <v>19</v>
+        <v>17</v>
+      </c>
+      <c r="C17" t="s">
+        <v>33</v>
       </c>
       <c r="D17">
-        <v>61</v>
+        <v>37</v>
       </c>
       <c r="E17">
-        <v>51</v>
+        <v>35</v>
       </c>
       <c r="F17">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="G17" s="1">
-        <v>83.59999999999999</v>
+        <v>94.59999999999999</v>
       </c>
       <c r="H17" s="1">
-        <v>16.4</v>
+        <v>5.4</v>
       </c>
       <c r="I17" s="2">
-        <v>7.4</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="J17">
         <v>0</v>
@@ -1106,31 +1106,28 @@
     </row>
     <row r="18" spans="1:11">
       <c r="A18" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B18" t="s">
         <v>18</v>
       </c>
-      <c r="C18" t="s">
-        <v>34</v>
-      </c>
       <c r="D18">
-        <v>28</v>
+        <v>113</v>
       </c>
       <c r="E18">
-        <v>27</v>
+        <v>108</v>
       </c>
       <c r="F18">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="G18" s="1">
-        <v>96.40000000000001</v>
+        <v>95.59999999999999</v>
       </c>
       <c r="H18" s="1">
-        <v>3.6</v>
+        <v>4.4</v>
       </c>
       <c r="I18" s="2">
-        <v>8.9</v>
+        <v>8.5</v>
       </c>
       <c r="J18">
         <v>0</v>
@@ -1146,23 +1143,26 @@
       <c r="B19" t="s">
         <v>19</v>
       </c>
+      <c r="C19" t="s">
+        <v>34</v>
+      </c>
       <c r="D19">
-        <v>28</v>
+        <v>40</v>
       </c>
       <c r="E19">
-        <v>27</v>
+        <v>34</v>
       </c>
       <c r="F19">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="G19" s="1">
-        <v>96.40000000000001</v>
+        <v>85</v>
       </c>
       <c r="H19" s="1">
-        <v>3.6</v>
+        <v>15</v>
       </c>
       <c r="I19" s="2">
-        <v>8.9</v>
+        <v>8.4</v>
       </c>
       <c r="J19">
         <v>0</v>
@@ -1173,31 +1173,31 @@
     </row>
     <row r="20" spans="1:11">
       <c r="A20" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B20" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C20" t="s">
         <v>35</v>
       </c>
       <c r="D20">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="E20">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="F20">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="G20" s="1">
-        <v>85</v>
+        <v>70.7</v>
       </c>
       <c r="H20" s="1">
-        <v>15</v>
+        <v>29.3</v>
       </c>
       <c r="I20" s="2">
-        <v>8.4</v>
+        <v>7.3</v>
       </c>
       <c r="J20">
         <v>0</v>
@@ -1208,31 +1208,31 @@
     </row>
     <row r="21" spans="1:11">
       <c r="A21" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B21" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C21" t="s">
         <v>36</v>
       </c>
       <c r="D21">
-        <v>41</v>
+        <v>48</v>
       </c>
       <c r="E21">
-        <v>29</v>
+        <v>45</v>
       </c>
       <c r="F21">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="G21" s="1">
-        <v>70.7</v>
+        <v>93.8</v>
       </c>
       <c r="H21" s="1">
-        <v>29.3</v>
+        <v>6.2</v>
       </c>
       <c r="I21" s="2">
-        <v>7.3</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="J21">
         <v>0</v>
@@ -1243,31 +1243,31 @@
     </row>
     <row r="22" spans="1:11">
       <c r="A22" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B22" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C22" t="s">
         <v>37</v>
       </c>
       <c r="D22">
-        <v>48</v>
+        <v>36</v>
       </c>
       <c r="E22">
-        <v>45</v>
+        <v>35</v>
       </c>
       <c r="F22">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G22" s="1">
-        <v>93.8</v>
+        <v>97.2</v>
       </c>
       <c r="H22" s="1">
-        <v>6.2</v>
+        <v>2.8</v>
       </c>
       <c r="I22" s="2">
-        <v>8.300000000000001</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="J22">
         <v>0</v>
@@ -1278,31 +1278,31 @@
     </row>
     <row r="23" spans="1:11">
       <c r="A23" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B23" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C23" t="s">
         <v>38</v>
       </c>
       <c r="D23">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E23">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="F23">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="G23" s="1">
-        <v>97.2</v>
+        <v>83.8</v>
       </c>
       <c r="H23" s="1">
-        <v>2.8</v>
+        <v>16.2</v>
       </c>
       <c r="I23" s="2">
-        <v>8.699999999999999</v>
+        <v>7.9</v>
       </c>
       <c r="J23">
         <v>0</v>
@@ -1313,31 +1313,31 @@
     </row>
     <row r="24" spans="1:11">
       <c r="A24" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B24" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C24" t="s">
         <v>39</v>
       </c>
       <c r="D24">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="E24">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="F24">
         <v>6</v>
       </c>
       <c r="G24" s="1">
-        <v>83.8</v>
+        <v>81.8</v>
       </c>
       <c r="H24" s="1">
-        <v>16.2</v>
+        <v>18.2</v>
       </c>
       <c r="I24" s="2">
-        <v>7.9</v>
+        <v>7.8</v>
       </c>
       <c r="J24">
         <v>0</v>
@@ -1348,31 +1348,31 @@
     </row>
     <row r="25" spans="1:11">
       <c r="A25" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B25" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="C25" t="s">
         <v>40</v>
       </c>
       <c r="D25">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="E25">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="F25">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G25" s="1">
-        <v>81.8</v>
+        <v>86.09999999999999</v>
       </c>
       <c r="H25" s="1">
-        <v>18.2</v>
+        <v>13.9</v>
       </c>
       <c r="I25" s="2">
-        <v>7.8</v>
+        <v>8.4</v>
       </c>
       <c r="J25">
         <v>0</v>
@@ -1383,31 +1383,31 @@
     </row>
     <row r="26" spans="1:11">
       <c r="A26" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B26" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C26" t="s">
         <v>41</v>
       </c>
       <c r="D26">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E26">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="F26">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="G26" s="1">
-        <v>86.09999999999999</v>
+        <v>94.3</v>
       </c>
       <c r="H26" s="1">
-        <v>13.9</v>
+        <v>5.7</v>
       </c>
       <c r="I26" s="2">
-        <v>8.4</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="J26">
         <v>0</v>
@@ -1418,31 +1418,28 @@
     </row>
     <row r="27" spans="1:11">
       <c r="A27" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B27" t="s">
         <v>18</v>
       </c>
-      <c r="C27" t="s">
-        <v>42</v>
-      </c>
       <c r="D27">
-        <v>35</v>
+        <v>306</v>
       </c>
       <c r="E27">
-        <v>33</v>
+        <v>265</v>
       </c>
       <c r="F27">
-        <v>2</v>
+        <v>41</v>
       </c>
       <c r="G27" s="1">
-        <v>94.3</v>
+        <v>86.59999999999999</v>
       </c>
       <c r="H27" s="1">
-        <v>5.7</v>
+        <v>13.4</v>
       </c>
       <c r="I27" s="2">
-        <v>8.699999999999999</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J27">
         <v>0</v>
@@ -1458,23 +1455,26 @@
       <c r="B28" t="s">
         <v>19</v>
       </c>
+      <c r="C28" t="s">
+        <v>42</v>
+      </c>
       <c r="D28">
-        <v>306</v>
+        <v>40</v>
       </c>
       <c r="E28">
-        <v>265</v>
+        <v>17</v>
       </c>
       <c r="F28">
-        <v>41</v>
+        <v>23</v>
       </c>
       <c r="G28" s="1">
-        <v>86.59999999999999</v>
+        <v>42.5</v>
       </c>
       <c r="H28" s="1">
-        <v>13.4</v>
+        <v>57.5</v>
       </c>
       <c r="I28" s="2">
-        <v>8.199999999999999</v>
+        <v>6</v>
       </c>
       <c r="J28">
         <v>0</v>
@@ -1485,13 +1485,10 @@
     </row>
     <row r="29" spans="1:11">
       <c r="A29" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B29" t="s">
-        <v>20</v>
-      </c>
-      <c r="C29" t="s">
-        <v>43</v>
+        <v>18</v>
       </c>
       <c r="D29">
         <v>40</v>
@@ -1519,63 +1516,31 @@
       </c>
     </row>
     <row r="30" spans="1:11">
-      <c r="A30" t="s">
-        <v>17</v>
-      </c>
       <c r="B30" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D30">
-        <v>40</v>
+        <v>664</v>
       </c>
       <c r="E30">
-        <v>17</v>
+        <v>555</v>
       </c>
       <c r="F30">
-        <v>23</v>
+        <v>109</v>
       </c>
       <c r="G30" s="1">
-        <v>42.5</v>
+        <v>83.59999999999999</v>
       </c>
       <c r="H30" s="1">
-        <v>57.5</v>
+        <v>16.4</v>
       </c>
       <c r="I30" s="2">
-        <v>6</v>
+        <v>7.6</v>
       </c>
       <c r="J30">
         <v>0</v>
       </c>
       <c r="K30" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="31" spans="1:11">
-      <c r="B31" t="s">
-        <v>21</v>
-      </c>
-      <c r="D31">
-        <v>664</v>
-      </c>
-      <c r="E31">
-        <v>555</v>
-      </c>
-      <c r="F31">
-        <v>109</v>
-      </c>
-      <c r="G31" s="1">
-        <v>83.59999999999999</v>
-      </c>
-      <c r="H31" s="1">
-        <v>16.4</v>
-      </c>
-      <c r="I31" s="2">
-        <v>7.6</v>
-      </c>
-      <c r="J31">
-        <v>0</v>
-      </c>
-      <c r="K31" s="1">
         <v>0</v>
       </c>
     </row>
@@ -1586,7 +1551,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:K31"/>
+  <dimension ref="A1:K30"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="2" width="30.7109375" customWidth="1"/>
@@ -1635,10 +1600,10 @@
         <v>11</v>
       </c>
       <c r="B2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C2" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D2">
         <v>10</v>
@@ -1670,7 +1635,7 @@
         <v>11</v>
       </c>
       <c r="B3" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D3">
         <v>10</v>
@@ -1702,28 +1667,28 @@
         <v>12</v>
       </c>
       <c r="B4" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D4">
-        <v>24</v>
+        <v>34</v>
       </c>
       <c r="E4">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="F4">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="G4" s="1">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="H4" s="1">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="I4" s="2">
-        <v>9.300000000000001</v>
+        <v>6.1</v>
       </c>
       <c r="J4">
         <v>0</v>
@@ -1737,28 +1702,28 @@
         <v>12</v>
       </c>
       <c r="B5" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C5" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D5">
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="E5">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="F5">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="G5" s="1">
-        <v>100</v>
+        <v>75.8</v>
       </c>
       <c r="H5" s="1">
-        <v>0</v>
+        <v>24.2</v>
       </c>
       <c r="I5" s="2">
-        <v>9.300000000000001</v>
+        <v>7.3</v>
       </c>
       <c r="J5">
         <v>0</v>
@@ -1772,28 +1737,28 @@
         <v>12</v>
       </c>
       <c r="B6" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C6" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D6">
-        <v>37</v>
+        <v>23</v>
       </c>
       <c r="E6">
-        <v>37</v>
+        <v>10</v>
       </c>
       <c r="F6">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="G6" s="1">
-        <v>100</v>
+        <v>43.5</v>
       </c>
       <c r="H6" s="1">
-        <v>0</v>
+        <v>56.5</v>
       </c>
       <c r="I6" s="2">
-        <v>9.300000000000001</v>
+        <v>5.8</v>
       </c>
       <c r="J6">
         <v>0</v>
@@ -1809,23 +1774,26 @@
       <c r="B7" t="s">
         <v>19</v>
       </c>
+      <c r="C7" t="s">
+        <v>25</v>
+      </c>
       <c r="D7">
-        <v>85</v>
+        <v>19</v>
       </c>
       <c r="E7">
-        <v>85</v>
+        <v>17</v>
       </c>
       <c r="F7">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G7" s="1">
-        <v>100</v>
+        <v>89.5</v>
       </c>
       <c r="H7" s="1">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="I7" s="2">
-        <v>9.300000000000001</v>
+        <v>7.4</v>
       </c>
       <c r="J7">
         <v>0</v>
@@ -1836,31 +1804,31 @@
     </row>
     <row r="8" spans="1:11">
       <c r="A8" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B8" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="C8" t="s">
         <v>26</v>
       </c>
       <c r="D8">
-        <v>34</v>
+        <v>25</v>
       </c>
       <c r="E8">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="F8">
-        <v>17</v>
+        <v>3</v>
       </c>
       <c r="G8" s="1">
-        <v>50</v>
+        <v>88</v>
       </c>
       <c r="H8" s="1">
-        <v>50</v>
+        <v>12</v>
       </c>
       <c r="I8" s="2">
-        <v>6.1</v>
+        <v>6.9</v>
       </c>
       <c r="J8">
         <v>0</v>
@@ -1871,31 +1839,28 @@
     </row>
     <row r="9" spans="1:11">
       <c r="A9" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B9" t="s">
-        <v>20</v>
-      </c>
-      <c r="C9" t="s">
-        <v>27</v>
+        <v>18</v>
       </c>
       <c r="D9">
-        <v>33</v>
+        <v>134</v>
       </c>
       <c r="E9">
-        <v>25</v>
+        <v>91</v>
       </c>
       <c r="F9">
-        <v>8</v>
+        <v>43</v>
       </c>
       <c r="G9" s="1">
-        <v>75.8</v>
+        <v>67.90000000000001</v>
       </c>
       <c r="H9" s="1">
-        <v>24.2</v>
+        <v>32.1</v>
       </c>
       <c r="I9" s="2">
-        <v>7.3</v>
+        <v>6.7</v>
       </c>
       <c r="J9">
         <v>0</v>
@@ -1909,28 +1874,28 @@
         <v>13</v>
       </c>
       <c r="B10" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="C10" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D10">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="E10">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="F10">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="G10" s="1">
-        <v>43.5</v>
+        <v>71.40000000000001</v>
       </c>
       <c r="H10" s="1">
-        <v>56.5</v>
+        <v>28.6</v>
       </c>
       <c r="I10" s="2">
-        <v>5.8</v>
+        <v>7.2</v>
       </c>
       <c r="J10">
         <v>0</v>
@@ -1944,10 +1909,10 @@
         <v>13</v>
       </c>
       <c r="B11" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="C11" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D11">
         <v>19</v>
@@ -1965,7 +1930,7 @@
         <v>10.5</v>
       </c>
       <c r="I11" s="2">
-        <v>7.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J11">
         <v>0</v>
@@ -1979,28 +1944,28 @@
         <v>13</v>
       </c>
       <c r="B12" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C12" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D12">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="E12">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="F12">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G12" s="1">
-        <v>88</v>
+        <v>90.5</v>
       </c>
       <c r="H12" s="1">
-        <v>12</v>
+        <v>9.5</v>
       </c>
       <c r="I12" s="2">
-        <v>6.9</v>
+        <v>8.1</v>
       </c>
       <c r="J12">
         <v>0</v>
@@ -2014,25 +1979,25 @@
         <v>13</v>
       </c>
       <c r="B13" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D13">
-        <v>134</v>
+        <v>61</v>
       </c>
       <c r="E13">
-        <v>91</v>
+        <v>51</v>
       </c>
       <c r="F13">
-        <v>43</v>
+        <v>10</v>
       </c>
       <c r="G13" s="1">
-        <v>67.90000000000001</v>
+        <v>83.59999999999999</v>
       </c>
       <c r="H13" s="1">
-        <v>32.1</v>
+        <v>16.4</v>
       </c>
       <c r="I13" s="2">
-        <v>6.7</v>
+        <v>7.8</v>
       </c>
       <c r="J13">
         <v>0</v>
@@ -2046,28 +2011,28 @@
         <v>14</v>
       </c>
       <c r="B14" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C14" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D14">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="E14">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="F14">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="G14" s="1">
-        <v>71.40000000000001</v>
+        <v>100</v>
       </c>
       <c r="H14" s="1">
-        <v>28.6</v>
+        <v>0</v>
       </c>
       <c r="I14" s="2">
-        <v>7.2</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="J14">
         <v>0</v>
@@ -2081,28 +2046,28 @@
         <v>14</v>
       </c>
       <c r="B15" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C15" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D15">
-        <v>19</v>
+        <v>28</v>
       </c>
       <c r="E15">
-        <v>17</v>
+        <v>27</v>
       </c>
       <c r="F15">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G15" s="1">
-        <v>89.5</v>
+        <v>96.40000000000001</v>
       </c>
       <c r="H15" s="1">
-        <v>10.5</v>
+        <v>3.6</v>
       </c>
       <c r="I15" s="2">
-        <v>8.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="J15">
         <v>0</v>
@@ -2116,28 +2081,28 @@
         <v>14</v>
       </c>
       <c r="B16" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C16" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D16">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="E16">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="F16">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G16" s="1">
-        <v>90.5</v>
+        <v>100</v>
       </c>
       <c r="H16" s="1">
-        <v>9.5</v>
+        <v>0</v>
       </c>
       <c r="I16" s="2">
-        <v>8.1</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="J16">
         <v>0</v>
@@ -2151,25 +2116,28 @@
         <v>14</v>
       </c>
       <c r="B17" t="s">
-        <v>19</v>
+        <v>17</v>
+      </c>
+      <c r="C17" t="s">
+        <v>33</v>
       </c>
       <c r="D17">
-        <v>61</v>
+        <v>37</v>
       </c>
       <c r="E17">
-        <v>51</v>
+        <v>37</v>
       </c>
       <c r="F17">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="G17" s="1">
-        <v>83.59999999999999</v>
+        <v>100</v>
       </c>
       <c r="H17" s="1">
-        <v>16.4</v>
+        <v>0</v>
       </c>
       <c r="I17" s="2">
-        <v>7.8</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="J17">
         <v>0</v>
@@ -2180,31 +2148,28 @@
     </row>
     <row r="18" spans="1:11">
       <c r="A18" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B18" t="s">
         <v>18</v>
       </c>
-      <c r="C18" t="s">
-        <v>34</v>
-      </c>
       <c r="D18">
-        <v>28</v>
+        <v>113</v>
       </c>
       <c r="E18">
-        <v>27</v>
+        <v>112</v>
       </c>
       <c r="F18">
         <v>1</v>
       </c>
       <c r="G18" s="1">
-        <v>96.40000000000001</v>
+        <v>99.09999999999999</v>
       </c>
       <c r="H18" s="1">
-        <v>3.6</v>
+        <v>0.9</v>
       </c>
       <c r="I18" s="2">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="J18">
         <v>0</v>
@@ -2220,23 +2185,26 @@
       <c r="B19" t="s">
         <v>19</v>
       </c>
+      <c r="C19" t="s">
+        <v>34</v>
+      </c>
       <c r="D19">
-        <v>28</v>
+        <v>40</v>
       </c>
       <c r="E19">
-        <v>27</v>
+        <v>36</v>
       </c>
       <c r="F19">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G19" s="1">
-        <v>96.40000000000001</v>
+        <v>90</v>
       </c>
       <c r="H19" s="1">
-        <v>3.6</v>
+        <v>10</v>
       </c>
       <c r="I19" s="2">
-        <v>9.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J19">
         <v>0</v>
@@ -2247,31 +2215,31 @@
     </row>
     <row r="20" spans="1:11">
       <c r="A20" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B20" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C20" t="s">
         <v>35</v>
       </c>
       <c r="D20">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="E20">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="F20">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="G20" s="1">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="H20" s="1">
-        <v>10</v>
+        <v>22</v>
       </c>
       <c r="I20" s="2">
-        <v>8.199999999999999</v>
+        <v>7.1</v>
       </c>
       <c r="J20">
         <v>0</v>
@@ -2282,31 +2250,31 @@
     </row>
     <row r="21" spans="1:11">
       <c r="A21" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B21" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C21" t="s">
         <v>36</v>
       </c>
       <c r="D21">
-        <v>41</v>
+        <v>48</v>
       </c>
       <c r="E21">
-        <v>32</v>
+        <v>44</v>
       </c>
       <c r="F21">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="G21" s="1">
-        <v>78</v>
+        <v>91.7</v>
       </c>
       <c r="H21" s="1">
-        <v>22</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="I21" s="2">
-        <v>7.1</v>
+        <v>7.6</v>
       </c>
       <c r="J21">
         <v>0</v>
@@ -2317,31 +2285,31 @@
     </row>
     <row r="22" spans="1:11">
       <c r="A22" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B22" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C22" t="s">
         <v>37</v>
       </c>
       <c r="D22">
-        <v>48</v>
+        <v>36</v>
       </c>
       <c r="E22">
-        <v>44</v>
+        <v>35</v>
       </c>
       <c r="F22">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G22" s="1">
-        <v>91.7</v>
+        <v>97.2</v>
       </c>
       <c r="H22" s="1">
+        <v>2.8</v>
+      </c>
+      <c r="I22" s="2">
         <v>8.300000000000001</v>
-      </c>
-      <c r="I22" s="2">
-        <v>7.6</v>
       </c>
       <c r="J22">
         <v>0</v>
@@ -2352,31 +2320,31 @@
     </row>
     <row r="23" spans="1:11">
       <c r="A23" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B23" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C23" t="s">
         <v>38</v>
       </c>
       <c r="D23">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E23">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="F23">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="G23" s="1">
-        <v>97.2</v>
+        <v>81.09999999999999</v>
       </c>
       <c r="H23" s="1">
-        <v>2.8</v>
+        <v>18.9</v>
       </c>
       <c r="I23" s="2">
-        <v>8.300000000000001</v>
+        <v>7.3</v>
       </c>
       <c r="J23">
         <v>0</v>
@@ -2387,31 +2355,31 @@
     </row>
     <row r="24" spans="1:11">
       <c r="A24" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B24" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C24" t="s">
         <v>39</v>
       </c>
       <c r="D24">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="E24">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="F24">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="G24" s="1">
-        <v>81.09999999999999</v>
+        <v>87.90000000000001</v>
       </c>
       <c r="H24" s="1">
-        <v>18.9</v>
+        <v>12.1</v>
       </c>
       <c r="I24" s="2">
-        <v>7.3</v>
+        <v>8.1</v>
       </c>
       <c r="J24">
         <v>0</v>
@@ -2422,31 +2390,31 @@
     </row>
     <row r="25" spans="1:11">
       <c r="A25" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B25" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="C25" t="s">
         <v>40</v>
       </c>
       <c r="D25">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="E25">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="F25">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G25" s="1">
-        <v>87.90000000000001</v>
+        <v>94.40000000000001</v>
       </c>
       <c r="H25" s="1">
-        <v>12.1</v>
+        <v>5.6</v>
       </c>
       <c r="I25" s="2">
-        <v>8.1</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="J25">
         <v>0</v>
@@ -2457,31 +2425,31 @@
     </row>
     <row r="26" spans="1:11">
       <c r="A26" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B26" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C26" t="s">
         <v>41</v>
       </c>
       <c r="D26">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E26">
         <v>34</v>
       </c>
       <c r="F26">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G26" s="1">
-        <v>94.40000000000001</v>
+        <v>97.09999999999999</v>
       </c>
       <c r="H26" s="1">
-        <v>5.6</v>
+        <v>2.9</v>
       </c>
       <c r="I26" s="2">
-        <v>8.300000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="J26">
         <v>0</v>
@@ -2492,31 +2460,28 @@
     </row>
     <row r="27" spans="1:11">
       <c r="A27" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B27" t="s">
         <v>18</v>
       </c>
-      <c r="C27" t="s">
-        <v>42</v>
-      </c>
       <c r="D27">
-        <v>35</v>
+        <v>306</v>
       </c>
       <c r="E27">
-        <v>34</v>
+        <v>274</v>
       </c>
       <c r="F27">
-        <v>1</v>
+        <v>32</v>
       </c>
       <c r="G27" s="1">
-        <v>97.09999999999999</v>
+        <v>89.5</v>
       </c>
       <c r="H27" s="1">
-        <v>2.9</v>
+        <v>10.5</v>
       </c>
       <c r="I27" s="2">
-        <v>8.6</v>
+        <v>7.9</v>
       </c>
       <c r="J27">
         <v>0</v>
@@ -2532,23 +2497,26 @@
       <c r="B28" t="s">
         <v>19</v>
       </c>
+      <c r="C28" t="s">
+        <v>42</v>
+      </c>
       <c r="D28">
-        <v>306</v>
+        <v>40</v>
       </c>
       <c r="E28">
-        <v>274</v>
+        <v>18</v>
       </c>
       <c r="F28">
-        <v>32</v>
+        <v>22</v>
       </c>
       <c r="G28" s="1">
-        <v>89.5</v>
+        <v>45</v>
       </c>
       <c r="H28" s="1">
-        <v>10.5</v>
+        <v>55</v>
       </c>
       <c r="I28" s="2">
-        <v>7.9</v>
+        <v>5.7</v>
       </c>
       <c r="J28">
         <v>0</v>
@@ -2559,13 +2527,10 @@
     </row>
     <row r="29" spans="1:11">
       <c r="A29" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B29" t="s">
-        <v>20</v>
-      </c>
-      <c r="C29" t="s">
-        <v>43</v>
+        <v>18</v>
       </c>
       <c r="D29">
         <v>40</v>
@@ -2593,63 +2558,31 @@
       </c>
     </row>
     <row r="30" spans="1:11">
-      <c r="A30" t="s">
-        <v>17</v>
-      </c>
       <c r="B30" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D30">
-        <v>40</v>
+        <v>664</v>
       </c>
       <c r="E30">
-        <v>18</v>
+        <v>556</v>
       </c>
       <c r="F30">
-        <v>22</v>
+        <v>108</v>
       </c>
       <c r="G30" s="1">
-        <v>45</v>
+        <v>83.7</v>
       </c>
       <c r="H30" s="1">
-        <v>55</v>
+        <v>16.3</v>
       </c>
       <c r="I30" s="2">
-        <v>5.7</v>
+        <v>7.9</v>
       </c>
       <c r="J30">
         <v>0</v>
       </c>
       <c r="K30" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="31" spans="1:11">
-      <c r="B31" t="s">
-        <v>21</v>
-      </c>
-      <c r="D31">
-        <v>664</v>
-      </c>
-      <c r="E31">
-        <v>556</v>
-      </c>
-      <c r="F31">
-        <v>108</v>
-      </c>
-      <c r="G31" s="1">
-        <v>83.7</v>
-      </c>
-      <c r="H31" s="1">
-        <v>16.3</v>
-      </c>
-      <c r="I31" s="2">
-        <v>7.9</v>
-      </c>
-      <c r="J31">
-        <v>0</v>
-      </c>
-      <c r="K31" s="1">
         <v>0</v>
       </c>
     </row>
@@ -2660,7 +2593,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:K31"/>
+  <dimension ref="A1:K30"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="2" width="30.7109375" customWidth="1"/>
@@ -2709,10 +2642,10 @@
         <v>11</v>
       </c>
       <c r="B2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C2" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D2">
         <v>10</v>
@@ -2744,7 +2677,7 @@
         <v>11</v>
       </c>
       <c r="B3" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D3">
         <v>10</v>
@@ -2776,28 +2709,28 @@
         <v>12</v>
       </c>
       <c r="B4" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D4">
-        <v>24</v>
+        <v>34</v>
       </c>
       <c r="E4">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="F4">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="G4" s="1">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="H4" s="1">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="I4" s="2">
-        <v>9.1</v>
+        <v>6.1</v>
       </c>
       <c r="J4">
         <v>0</v>
@@ -2811,28 +2744,28 @@
         <v>12</v>
       </c>
       <c r="B5" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C5" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D5">
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="E5">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="F5">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="G5" s="1">
-        <v>100</v>
+        <v>75.8</v>
       </c>
       <c r="H5" s="1">
-        <v>0</v>
+        <v>24.2</v>
       </c>
       <c r="I5" s="2">
-        <v>9</v>
+        <v>6.9</v>
       </c>
       <c r="J5">
         <v>0</v>
@@ -2846,28 +2779,28 @@
         <v>12</v>
       </c>
       <c r="B6" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C6" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D6">
-        <v>37</v>
+        <v>23</v>
       </c>
       <c r="E6">
-        <v>37</v>
+        <v>10</v>
       </c>
       <c r="F6">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="G6" s="1">
-        <v>100</v>
+        <v>43.5</v>
       </c>
       <c r="H6" s="1">
-        <v>0</v>
+        <v>56.5</v>
       </c>
       <c r="I6" s="2">
-        <v>9.1</v>
+        <v>5.9</v>
       </c>
       <c r="J6">
         <v>0</v>
@@ -2883,23 +2816,26 @@
       <c r="B7" t="s">
         <v>19</v>
       </c>
+      <c r="C7" t="s">
+        <v>25</v>
+      </c>
       <c r="D7">
-        <v>85</v>
+        <v>19</v>
       </c>
       <c r="E7">
-        <v>85</v>
+        <v>17</v>
       </c>
       <c r="F7">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G7" s="1">
-        <v>100</v>
+        <v>89.5</v>
       </c>
       <c r="H7" s="1">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="I7" s="2">
-        <v>9.1</v>
+        <v>7.3</v>
       </c>
       <c r="J7">
         <v>0</v>
@@ -2910,31 +2846,31 @@
     </row>
     <row r="8" spans="1:11">
       <c r="A8" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B8" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="C8" t="s">
         <v>26</v>
       </c>
       <c r="D8">
-        <v>34</v>
+        <v>25</v>
       </c>
       <c r="E8">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="F8">
-        <v>17</v>
+        <v>3</v>
       </c>
       <c r="G8" s="1">
-        <v>50</v>
+        <v>88</v>
       </c>
       <c r="H8" s="1">
-        <v>50</v>
+        <v>12</v>
       </c>
       <c r="I8" s="2">
-        <v>6.1</v>
+        <v>7.3</v>
       </c>
       <c r="J8">
         <v>0</v>
@@ -2945,31 +2881,28 @@
     </row>
     <row r="9" spans="1:11">
       <c r="A9" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B9" t="s">
-        <v>20</v>
-      </c>
-      <c r="C9" t="s">
-        <v>27</v>
+        <v>18</v>
       </c>
       <c r="D9">
-        <v>33</v>
+        <v>134</v>
       </c>
       <c r="E9">
-        <v>25</v>
+        <v>91</v>
       </c>
       <c r="F9">
-        <v>8</v>
+        <v>43</v>
       </c>
       <c r="G9" s="1">
-        <v>75.8</v>
+        <v>67.90000000000001</v>
       </c>
       <c r="H9" s="1">
-        <v>24.2</v>
+        <v>32.1</v>
       </c>
       <c r="I9" s="2">
-        <v>6.9</v>
+        <v>6.7</v>
       </c>
       <c r="J9">
         <v>0</v>
@@ -2983,28 +2916,28 @@
         <v>13</v>
       </c>
       <c r="B10" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="C10" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D10">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="E10">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="F10">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="G10" s="1">
-        <v>43.5</v>
+        <v>71.40000000000001</v>
       </c>
       <c r="H10" s="1">
-        <v>56.5</v>
+        <v>28.6</v>
       </c>
       <c r="I10" s="2">
-        <v>5.9</v>
+        <v>6.9</v>
       </c>
       <c r="J10">
         <v>0</v>
@@ -3018,10 +2951,10 @@
         <v>13</v>
       </c>
       <c r="B11" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="C11" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D11">
         <v>19</v>
@@ -3039,7 +2972,7 @@
         <v>10.5</v>
       </c>
       <c r="I11" s="2">
-        <v>7.3</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="J11">
         <v>0</v>
@@ -3053,28 +2986,28 @@
         <v>13</v>
       </c>
       <c r="B12" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C12" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D12">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="E12">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="F12">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G12" s="1">
-        <v>88</v>
+        <v>90.5</v>
       </c>
       <c r="H12" s="1">
-        <v>12</v>
+        <v>9.5</v>
       </c>
       <c r="I12" s="2">
-        <v>7.3</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J12">
         <v>0</v>
@@ -3088,25 +3021,25 @@
         <v>13</v>
       </c>
       <c r="B13" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D13">
-        <v>134</v>
+        <v>61</v>
       </c>
       <c r="E13">
-        <v>91</v>
+        <v>51</v>
       </c>
       <c r="F13">
-        <v>43</v>
+        <v>10</v>
       </c>
       <c r="G13" s="1">
-        <v>67.90000000000001</v>
+        <v>83.59999999999999</v>
       </c>
       <c r="H13" s="1">
-        <v>32.1</v>
+        <v>16.4</v>
       </c>
       <c r="I13" s="2">
-        <v>6.7</v>
+        <v>7.8</v>
       </c>
       <c r="J13">
         <v>0</v>
@@ -3120,28 +3053,28 @@
         <v>14</v>
       </c>
       <c r="B14" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C14" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D14">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="E14">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="F14">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="G14" s="1">
-        <v>71.40000000000001</v>
+        <v>100</v>
       </c>
       <c r="H14" s="1">
-        <v>28.6</v>
+        <v>0</v>
       </c>
       <c r="I14" s="2">
-        <v>6.9</v>
+        <v>9.1</v>
       </c>
       <c r="J14">
         <v>0</v>
@@ -3155,28 +3088,28 @@
         <v>14</v>
       </c>
       <c r="B15" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C15" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D15">
-        <v>19</v>
+        <v>28</v>
       </c>
       <c r="E15">
-        <v>17</v>
+        <v>27</v>
       </c>
       <c r="F15">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G15" s="1">
-        <v>89.5</v>
+        <v>96.40000000000001</v>
       </c>
       <c r="H15" s="1">
-        <v>10.5</v>
+        <v>3.6</v>
       </c>
       <c r="I15" s="2">
-        <v>8.300000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="J15">
         <v>0</v>
@@ -3190,28 +3123,28 @@
         <v>14</v>
       </c>
       <c r="B16" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C16" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D16">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="E16">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="F16">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G16" s="1">
-        <v>90.5</v>
+        <v>100</v>
       </c>
       <c r="H16" s="1">
-        <v>9.5</v>
+        <v>0</v>
       </c>
       <c r="I16" s="2">
-        <v>8.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="J16">
         <v>0</v>
@@ -3225,25 +3158,28 @@
         <v>14</v>
       </c>
       <c r="B17" t="s">
-        <v>19</v>
+        <v>17</v>
+      </c>
+      <c r="C17" t="s">
+        <v>33</v>
       </c>
       <c r="D17">
-        <v>61</v>
+        <v>37</v>
       </c>
       <c r="E17">
-        <v>51</v>
+        <v>37</v>
       </c>
       <c r="F17">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="G17" s="1">
-        <v>83.59999999999999</v>
+        <v>100</v>
       </c>
       <c r="H17" s="1">
-        <v>16.4</v>
+        <v>0</v>
       </c>
       <c r="I17" s="2">
-        <v>7.8</v>
+        <v>9.1</v>
       </c>
       <c r="J17">
         <v>0</v>
@@ -3254,31 +3190,28 @@
     </row>
     <row r="18" spans="1:11">
       <c r="A18" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B18" t="s">
         <v>18</v>
       </c>
-      <c r="C18" t="s">
-        <v>34</v>
-      </c>
       <c r="D18">
-        <v>28</v>
+        <v>113</v>
       </c>
       <c r="E18">
-        <v>27</v>
+        <v>112</v>
       </c>
       <c r="F18">
         <v>1</v>
       </c>
       <c r="G18" s="1">
-        <v>96.40000000000001</v>
+        <v>99.09999999999999</v>
       </c>
       <c r="H18" s="1">
-        <v>3.6</v>
+        <v>0.9</v>
       </c>
       <c r="I18" s="2">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="J18">
         <v>0</v>
@@ -3294,23 +3227,26 @@
       <c r="B19" t="s">
         <v>19</v>
       </c>
+      <c r="C19" t="s">
+        <v>34</v>
+      </c>
       <c r="D19">
-        <v>28</v>
+        <v>40</v>
       </c>
       <c r="E19">
-        <v>27</v>
+        <v>36</v>
       </c>
       <c r="F19">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G19" s="1">
-        <v>96.40000000000001</v>
+        <v>90</v>
       </c>
       <c r="H19" s="1">
-        <v>3.6</v>
+        <v>10</v>
       </c>
       <c r="I19" s="2">
-        <v>9.4</v>
+        <v>8.5</v>
       </c>
       <c r="J19">
         <v>0</v>
@@ -3321,31 +3257,31 @@
     </row>
     <row r="20" spans="1:11">
       <c r="A20" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B20" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C20" t="s">
         <v>35</v>
       </c>
       <c r="D20">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="E20">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="F20">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="G20" s="1">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="H20" s="1">
-        <v>10</v>
+        <v>22</v>
       </c>
       <c r="I20" s="2">
-        <v>8.5</v>
+        <v>7.4</v>
       </c>
       <c r="J20">
         <v>0</v>
@@ -3356,31 +3292,31 @@
     </row>
     <row r="21" spans="1:11">
       <c r="A21" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B21" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C21" t="s">
         <v>36</v>
       </c>
       <c r="D21">
-        <v>41</v>
+        <v>48</v>
       </c>
       <c r="E21">
-        <v>32</v>
+        <v>44</v>
       </c>
       <c r="F21">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="G21" s="1">
-        <v>78</v>
+        <v>91.7</v>
       </c>
       <c r="H21" s="1">
-        <v>22</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="I21" s="2">
-        <v>7.4</v>
+        <v>8.1</v>
       </c>
       <c r="J21">
         <v>0</v>
@@ -3391,31 +3327,31 @@
     </row>
     <row r="22" spans="1:11">
       <c r="A22" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B22" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C22" t="s">
         <v>37</v>
       </c>
       <c r="D22">
-        <v>48</v>
+        <v>36</v>
       </c>
       <c r="E22">
-        <v>44</v>
+        <v>35</v>
       </c>
       <c r="F22">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G22" s="1">
-        <v>91.7</v>
+        <v>97.2</v>
       </c>
       <c r="H22" s="1">
-        <v>8.300000000000001</v>
+        <v>2.8</v>
       </c>
       <c r="I22" s="2">
-        <v>8.1</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="J22">
         <v>0</v>
@@ -3426,31 +3362,31 @@
     </row>
     <row r="23" spans="1:11">
       <c r="A23" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B23" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C23" t="s">
         <v>38</v>
       </c>
       <c r="D23">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E23">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="F23">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="G23" s="1">
-        <v>97.2</v>
+        <v>81.09999999999999</v>
       </c>
       <c r="H23" s="1">
-        <v>2.8</v>
+        <v>18.9</v>
       </c>
       <c r="I23" s="2">
-        <v>8.699999999999999</v>
+        <v>7.8</v>
       </c>
       <c r="J23">
         <v>0</v>
@@ -3461,31 +3397,31 @@
     </row>
     <row r="24" spans="1:11">
       <c r="A24" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B24" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C24" t="s">
         <v>39</v>
       </c>
       <c r="D24">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="E24">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="F24">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="G24" s="1">
-        <v>81.09999999999999</v>
+        <v>87.90000000000001</v>
       </c>
       <c r="H24" s="1">
-        <v>18.9</v>
+        <v>12.1</v>
       </c>
       <c r="I24" s="2">
-        <v>7.8</v>
+        <v>8.1</v>
       </c>
       <c r="J24">
         <v>0</v>
@@ -3496,31 +3432,31 @@
     </row>
     <row r="25" spans="1:11">
       <c r="A25" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B25" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="C25" t="s">
         <v>40</v>
       </c>
       <c r="D25">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="E25">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="F25">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G25" s="1">
-        <v>87.90000000000001</v>
+        <v>94.40000000000001</v>
       </c>
       <c r="H25" s="1">
-        <v>12.1</v>
+        <v>5.6</v>
       </c>
       <c r="I25" s="2">
-        <v>8.1</v>
+        <v>8.6</v>
       </c>
       <c r="J25">
         <v>0</v>
@@ -3531,31 +3467,31 @@
     </row>
     <row r="26" spans="1:11">
       <c r="A26" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B26" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C26" t="s">
         <v>41</v>
       </c>
       <c r="D26">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E26">
         <v>34</v>
       </c>
       <c r="F26">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G26" s="1">
-        <v>94.40000000000001</v>
+        <v>97.09999999999999</v>
       </c>
       <c r="H26" s="1">
-        <v>5.6</v>
+        <v>2.9</v>
       </c>
       <c r="I26" s="2">
-        <v>8.6</v>
+        <v>8.9</v>
       </c>
       <c r="J26">
         <v>0</v>
@@ -3566,31 +3502,28 @@
     </row>
     <row r="27" spans="1:11">
       <c r="A27" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B27" t="s">
         <v>18</v>
       </c>
-      <c r="C27" t="s">
-        <v>42</v>
-      </c>
       <c r="D27">
-        <v>35</v>
+        <v>306</v>
       </c>
       <c r="E27">
-        <v>34</v>
+        <v>274</v>
       </c>
       <c r="F27">
-        <v>1</v>
+        <v>32</v>
       </c>
       <c r="G27" s="1">
-        <v>97.09999999999999</v>
+        <v>89.5</v>
       </c>
       <c r="H27" s="1">
-        <v>2.9</v>
+        <v>10.5</v>
       </c>
       <c r="I27" s="2">
-        <v>8.9</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="J27">
         <v>0</v>
@@ -3606,23 +3539,26 @@
       <c r="B28" t="s">
         <v>19</v>
       </c>
+      <c r="C28" t="s">
+        <v>42</v>
+      </c>
       <c r="D28">
-        <v>306</v>
+        <v>40</v>
       </c>
       <c r="E28">
-        <v>274</v>
+        <v>18</v>
       </c>
       <c r="F28">
-        <v>32</v>
+        <v>22</v>
       </c>
       <c r="G28" s="1">
-        <v>89.5</v>
+        <v>45</v>
       </c>
       <c r="H28" s="1">
-        <v>10.5</v>
+        <v>55</v>
       </c>
       <c r="I28" s="2">
-        <v>8.300000000000001</v>
+        <v>5.8</v>
       </c>
       <c r="J28">
         <v>0</v>
@@ -3633,13 +3569,10 @@
     </row>
     <row r="29" spans="1:11">
       <c r="A29" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B29" t="s">
-        <v>20</v>
-      </c>
-      <c r="C29" t="s">
-        <v>43</v>
+        <v>18</v>
       </c>
       <c r="D29">
         <v>40</v>
@@ -3667,63 +3600,31 @@
       </c>
     </row>
     <row r="30" spans="1:11">
-      <c r="A30" t="s">
-        <v>17</v>
-      </c>
       <c r="B30" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D30">
-        <v>40</v>
+        <v>664</v>
       </c>
       <c r="E30">
-        <v>18</v>
+        <v>556</v>
       </c>
       <c r="F30">
-        <v>22</v>
+        <v>108</v>
       </c>
       <c r="G30" s="1">
-        <v>45</v>
+        <v>83.7</v>
       </c>
       <c r="H30" s="1">
-        <v>55</v>
+        <v>16.3</v>
       </c>
       <c r="I30" s="2">
-        <v>5.8</v>
+        <v>7.9</v>
       </c>
       <c r="J30">
         <v>0</v>
       </c>
       <c r="K30" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="31" spans="1:11">
-      <c r="B31" t="s">
-        <v>21</v>
-      </c>
-      <c r="D31">
-        <v>664</v>
-      </c>
-      <c r="E31">
-        <v>556</v>
-      </c>
-      <c r="F31">
-        <v>108</v>
-      </c>
-      <c r="G31" s="1">
-        <v>83.7</v>
-      </c>
-      <c r="H31" s="1">
-        <v>16.3</v>
-      </c>
-      <c r="I31" s="2">
-        <v>7.9</v>
-      </c>
-      <c r="J31">
-        <v>0</v>
-      </c>
-      <c r="K31" s="1">
         <v>0</v>
       </c>
     </row>

--- a/academias/Humanidades - Estadisticos 20241.xlsx
+++ b/academias/Humanidades - Estadisticos 20241.xlsx
@@ -2239,7 +2239,7 @@
         <v>22</v>
       </c>
       <c r="I20" s="2">
-        <v>7.1</v>
+        <v>7.2</v>
       </c>
       <c r="J20">
         <v>0</v>
@@ -2481,7 +2481,7 @@
         <v>10.5</v>
       </c>
       <c r="I27" s="2">
-        <v>7.9</v>
+        <v>8</v>
       </c>
       <c r="J27">
         <v>0</v>
@@ -2718,19 +2718,19 @@
         <v>34</v>
       </c>
       <c r="E4">
-        <v>17</v>
+        <v>26</v>
       </c>
       <c r="F4">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="G4" s="1">
-        <v>50</v>
+        <v>76.5</v>
       </c>
       <c r="H4" s="1">
-        <v>50</v>
+        <v>23.5</v>
       </c>
       <c r="I4" s="2">
-        <v>6.1</v>
+        <v>6.3</v>
       </c>
       <c r="J4">
         <v>0</v>
@@ -2753,19 +2753,19 @@
         <v>33</v>
       </c>
       <c r="E5">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F5">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G5" s="1">
-        <v>75.8</v>
+        <v>78.8</v>
       </c>
       <c r="H5" s="1">
-        <v>24.2</v>
+        <v>21.2</v>
       </c>
       <c r="I5" s="2">
-        <v>6.9</v>
+        <v>6.8</v>
       </c>
       <c r="J5">
         <v>0</v>
@@ -2788,19 +2788,19 @@
         <v>23</v>
       </c>
       <c r="E6">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="F6">
+        <v>3</v>
+      </c>
+      <c r="G6" s="1">
+        <v>87</v>
+      </c>
+      <c r="H6" s="1">
         <v>13</v>
       </c>
-      <c r="G6" s="1">
-        <v>43.5</v>
-      </c>
-      <c r="H6" s="1">
-        <v>56.5</v>
-      </c>
       <c r="I6" s="2">
-        <v>5.9</v>
+        <v>6.3</v>
       </c>
       <c r="J6">
         <v>0</v>
@@ -2823,19 +2823,19 @@
         <v>19</v>
       </c>
       <c r="E7">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="F7">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G7" s="1">
-        <v>89.5</v>
+        <v>100</v>
       </c>
       <c r="H7" s="1">
-        <v>10.5</v>
+        <v>0</v>
       </c>
       <c r="I7" s="2">
-        <v>7.3</v>
+        <v>7.2</v>
       </c>
       <c r="J7">
         <v>0</v>
@@ -2858,19 +2858,19 @@
         <v>25</v>
       </c>
       <c r="E8">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F8">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G8" s="1">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="H8" s="1">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="I8" s="2">
-        <v>7.3</v>
+        <v>7</v>
       </c>
       <c r="J8">
         <v>0</v>
@@ -2890,16 +2890,16 @@
         <v>134</v>
       </c>
       <c r="E9">
-        <v>91</v>
+        <v>114</v>
       </c>
       <c r="F9">
-        <v>43</v>
+        <v>20</v>
       </c>
       <c r="G9" s="1">
-        <v>67.90000000000001</v>
+        <v>85.09999999999999</v>
       </c>
       <c r="H9" s="1">
-        <v>32.1</v>
+        <v>14.9</v>
       </c>
       <c r="I9" s="2">
         <v>6.7</v>
@@ -3109,7 +3109,7 @@
         <v>3.6</v>
       </c>
       <c r="I15" s="2">
-        <v>9.4</v>
+        <v>9.1</v>
       </c>
       <c r="J15">
         <v>0</v>
@@ -3144,7 +3144,7 @@
         <v>0</v>
       </c>
       <c r="I16" s="2">
-        <v>9</v>
+        <v>8.9</v>
       </c>
       <c r="J16">
         <v>0</v>
@@ -3211,7 +3211,7 @@
         <v>0.9</v>
       </c>
       <c r="I18" s="2">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="J18">
         <v>0</v>
@@ -3234,16 +3234,16 @@
         <v>40</v>
       </c>
       <c r="E19">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="F19">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G19" s="1">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="H19" s="1">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="I19" s="2">
         <v>8.5</v>
@@ -3269,19 +3269,19 @@
         <v>41</v>
       </c>
       <c r="E20">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="F20">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="G20" s="1">
-        <v>78</v>
+        <v>92.7</v>
       </c>
       <c r="H20" s="1">
-        <v>22</v>
+        <v>7.3</v>
       </c>
       <c r="I20" s="2">
-        <v>7.4</v>
+        <v>7.7</v>
       </c>
       <c r="J20">
         <v>0</v>
@@ -3304,19 +3304,19 @@
         <v>48</v>
       </c>
       <c r="E21">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="F21">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G21" s="1">
-        <v>91.7</v>
+        <v>95.8</v>
       </c>
       <c r="H21" s="1">
-        <v>8.300000000000001</v>
+        <v>4.2</v>
       </c>
       <c r="I21" s="2">
-        <v>8.1</v>
+        <v>8.4</v>
       </c>
       <c r="J21">
         <v>0</v>
@@ -3351,7 +3351,7 @@
         <v>2.8</v>
       </c>
       <c r="I22" s="2">
-        <v>8.699999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="J22">
         <v>0</v>
@@ -3374,19 +3374,19 @@
         <v>37</v>
       </c>
       <c r="E23">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="F23">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="G23" s="1">
-        <v>81.09999999999999</v>
+        <v>94.59999999999999</v>
       </c>
       <c r="H23" s="1">
-        <v>18.9</v>
+        <v>5.4</v>
       </c>
       <c r="I23" s="2">
-        <v>7.8</v>
+        <v>8.1</v>
       </c>
       <c r="J23">
         <v>0</v>
@@ -3409,19 +3409,19 @@
         <v>33</v>
       </c>
       <c r="E24">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="F24">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G24" s="1">
-        <v>87.90000000000001</v>
+        <v>97</v>
       </c>
       <c r="H24" s="1">
-        <v>12.1</v>
+        <v>3</v>
       </c>
       <c r="I24" s="2">
-        <v>8.1</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J24">
         <v>0</v>
@@ -3444,19 +3444,19 @@
         <v>36</v>
       </c>
       <c r="E25">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="F25">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G25" s="1">
-        <v>94.40000000000001</v>
+        <v>100</v>
       </c>
       <c r="H25" s="1">
-        <v>5.6</v>
+        <v>0</v>
       </c>
       <c r="I25" s="2">
-        <v>8.6</v>
+        <v>8.5</v>
       </c>
       <c r="J25">
         <v>0</v>
@@ -3511,19 +3511,19 @@
         <v>306</v>
       </c>
       <c r="E27">
-        <v>274</v>
+        <v>294</v>
       </c>
       <c r="F27">
-        <v>32</v>
+        <v>12</v>
       </c>
       <c r="G27" s="1">
-        <v>89.5</v>
+        <v>96.09999999999999</v>
       </c>
       <c r="H27" s="1">
-        <v>10.5</v>
+        <v>3.9</v>
       </c>
       <c r="I27" s="2">
-        <v>8.300000000000001</v>
+        <v>8.4</v>
       </c>
       <c r="J27">
         <v>0</v>
@@ -3607,19 +3607,19 @@
         <v>664</v>
       </c>
       <c r="E30">
-        <v>556</v>
+        <v>599</v>
       </c>
       <c r="F30">
-        <v>108</v>
+        <v>65</v>
       </c>
       <c r="G30" s="1">
-        <v>83.7</v>
+        <v>90.2</v>
       </c>
       <c r="H30" s="1">
-        <v>16.3</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="I30" s="2">
-        <v>7.9</v>
+        <v>8</v>
       </c>
       <c r="J30">
         <v>0</v>

--- a/academias/Humanidades - Estadisticos 20241.xlsx
+++ b/academias/Humanidades - Estadisticos 20241.xlsx
@@ -2925,19 +2925,19 @@
         <v>21</v>
       </c>
       <c r="E10">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="F10">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="G10" s="1">
-        <v>71.40000000000001</v>
+        <v>85.7</v>
       </c>
       <c r="H10" s="1">
-        <v>28.6</v>
+        <v>14.3</v>
       </c>
       <c r="I10" s="2">
-        <v>6.9</v>
+        <v>7</v>
       </c>
       <c r="J10">
         <v>0</v>
@@ -2960,19 +2960,19 @@
         <v>19</v>
       </c>
       <c r="E11">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F11">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G11" s="1">
-        <v>89.5</v>
+        <v>94.7</v>
       </c>
       <c r="H11" s="1">
-        <v>10.5</v>
+        <v>5.3</v>
       </c>
       <c r="I11" s="2">
-        <v>8.300000000000001</v>
+        <v>8</v>
       </c>
       <c r="J11">
         <v>0</v>
@@ -2995,19 +2995,19 @@
         <v>21</v>
       </c>
       <c r="E12">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F12">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G12" s="1">
-        <v>90.5</v>
+        <v>95.2</v>
       </c>
       <c r="H12" s="1">
-        <v>9.5</v>
+        <v>4.8</v>
       </c>
       <c r="I12" s="2">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="J12">
         <v>0</v>
@@ -3027,19 +3027,19 @@
         <v>61</v>
       </c>
       <c r="E13">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="F13">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="G13" s="1">
-        <v>83.59999999999999</v>
+        <v>91.8</v>
       </c>
       <c r="H13" s="1">
-        <v>16.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="I13" s="2">
-        <v>7.8</v>
+        <v>7.7</v>
       </c>
       <c r="J13">
         <v>0</v>
@@ -3546,19 +3546,19 @@
         <v>40</v>
       </c>
       <c r="E28">
-        <v>18</v>
+        <v>29</v>
       </c>
       <c r="F28">
-        <v>22</v>
+        <v>11</v>
       </c>
       <c r="G28" s="1">
-        <v>45</v>
+        <v>72.5</v>
       </c>
       <c r="H28" s="1">
-        <v>55</v>
+        <v>27.5</v>
       </c>
       <c r="I28" s="2">
-        <v>5.8</v>
+        <v>6.1</v>
       </c>
       <c r="J28">
         <v>0</v>
@@ -3578,19 +3578,19 @@
         <v>40</v>
       </c>
       <c r="E29">
-        <v>18</v>
+        <v>29</v>
       </c>
       <c r="F29">
-        <v>22</v>
+        <v>11</v>
       </c>
       <c r="G29" s="1">
-        <v>45</v>
+        <v>72.5</v>
       </c>
       <c r="H29" s="1">
-        <v>55</v>
+        <v>27.5</v>
       </c>
       <c r="I29" s="2">
-        <v>5.8</v>
+        <v>6.1</v>
       </c>
       <c r="J29">
         <v>0</v>
@@ -3607,16 +3607,16 @@
         <v>664</v>
       </c>
       <c r="E30">
-        <v>599</v>
+        <v>615</v>
       </c>
       <c r="F30">
-        <v>65</v>
+        <v>49</v>
       </c>
       <c r="G30" s="1">
-        <v>90.2</v>
+        <v>92.59999999999999</v>
       </c>
       <c r="H30" s="1">
-        <v>9.800000000000001</v>
+        <v>7.4</v>
       </c>
       <c r="I30" s="2">
         <v>8</v>
